--- a/docs/03_詳細設計/01_オンライン設計/KF-DD-ONL-010_承認_オンライン詳細設計書.xlsx
+++ b/docs/03_詳細設計/01_オンライン設計/KF-DD-ONL-010_承認_オンライン詳細設計書.xlsx
@@ -333,7 +333,7 @@
       <row>19</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8572500" cy="18049875"/>
+    <ext cx="8572500" cy="18259425"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -765,7 +765,7 @@
     <row r="17">
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>本書の位置づけ：KF-DD-001 は全オンライン処理(ONL-001〜022)の概要。本書はそのうち ONL-010 を実装レベルまで詳細化したもの。
+          <t>本書の位置づけ：KF-DD-001 は全オンライン処理(ONL-001〜023)の概要。本書はそのうち ONL-010 を実装レベルまで詳細化したもの。
 本書の目的：本書だけを見て、この処理のバックエンドを実装・単体テストできる粒度で記述する。</t>
         </is>
       </c>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="E2" s="7" t="inlineStr"/>
     </row>
-    <row r="3" ht="109" customHeight="1">
+    <row r="3" ht="184" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
           <t>1.1</t>
@@ -2315,7 +2315,9 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>・確定設計変更 D1〜D10 を反映：通知を notify 4引数・NotificationType（REQUEST_APPROVED / REQUEST_SUBMITTED）に統一し type / request_id を保存、updated_at をトリガ自動更新とし native UPDATE から updated_at = :now を削除（updateStatusIfPending / advanceStepIfPending から now 引数を削除）、tables の attendance_records を C/R/U 表記に統一、差戻し再提出は ONL-022 に変更、SecurityConfig 前提を共通基盤の追加改修に合わせて更新</t>
+          <t>・確定設計変更 D1〜D10 を反映：通知を notify 4引数・NotificationType（REQUEST_APPROVED / REQUEST_SUBMITTED）に統一し type / request_id を保存、updated_at をトリガ自動更新とし native UPDATE から updated_at = :now を削除（updateStatusIfPending / advanceStepIfPending から now 引数を削除）、tables の attendance_records を C/R/U 表記に統一、差戻し再提出は ONL-022 に変更、SecurityConfig 前提を共通基盤の追加改修に合わせて更新
+・実装に合わせて逆反映：Controller は Authentication#getName() でユーザーIDを取得、日時は Clock Bean（Asia/Tokyo）注入（コードを正とする）
+・日付項目は LocalDate のまま返し yyyy-MM-dd で出力。submittedAt / step1ApprovedAt は AppTime.toIso の文字列</t>
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr"/>
@@ -4051,7 +4053,7 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>UPDATE approval_steps SET status='APPROVED', approver_id=実行者, comment, acted_at=now(JST) WHERE id=? AND status='WAITING'（updated_at は DB トリガで自動更新）</t>
+          <t>UPDATE approval_steps SET status='APPROVED', approver_id=実行者, comment, acted_at=now(clock) WHERE id=? AND status='WAITING'（updated_at は DB トリガで自動更新）</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
@@ -4326,7 +4328,7 @@
       </c>
       <c r="B4" s="12" t="inlineStr">
         <is>
-          <t>public ApprovalResultResponse approve(@PathVariable("id") Long id, @Valid @RequestBody(required = false) ApprovalCommentRequest request, @AuthenticationPrincipal Jwt jwt)</t>
+          <t>public ApprovalResultResponse approve(@PathVariable("id") Long id, @Valid @RequestBody(required = false) ApprovalCommentRequest request, Authentication auth)</t>
         </is>
       </c>
       <c r="C4" s="9" t="n"/>
@@ -4430,17 +4432,17 @@
     <row r="10" ht="19" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>jwt</t>
+          <t>auth</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Jwt</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>認証済みトークン。sub＝users.id</t>
+          <t>認証情報（Spring Security が注入）。getName() = users.id（JWT の sub）</t>
         </is>
       </c>
       <c r="D10" s="9" t="n"/>
@@ -4493,7 +4495,7 @@
           <t>1. Spring Security が Bearer トークンを検証する（無効・期限切れ → 401）
 2. @PreAuthorize でロール（ROLE_MANAGER / ROLE_ADMIN）を確認する
 3. @Valid で ApprovalCommentRequest を検証する（body 省略時は検証されない）
-4. userId = Long.valueOf(jwt.getSubject());
+4. userId = Long.valueOf(auth.getName());
 5. comment = (request == null) ? null : request.comment();
 6. return approvalService.approve(id, userId, comment);</t>
         </is>

--- a/docs/03_詳細設計/01_オンライン設計/KF-DD-ONL-010_承認_オンライン詳細設計書.xlsx
+++ b/docs/03_詳細設計/01_オンライン設計/KF-DD-ONL-010_承認_オンライン詳細設計書.xlsx
@@ -273,7 +273,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10953750" cy="4981575"/>
+    <ext cx="10953750" cy="6324600"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -333,7 +333,7 @@
       <row>19</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8572500" cy="18259425"/>
+    <ext cx="8572500" cy="18669000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -722,7 +722,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.2</t>
         </is>
       </c>
     </row>
@@ -765,7 +765,7 @@
     <row r="17">
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>本書の位置づけ：KF-DD-001 は全オンライン処理(ONL-001〜023)の概要。本書はそのうち ONL-010 を実装レベルまで詳細化したもの。
+          <t>本書の位置づけ：KF-DD-001 は全オンライン処理(ONL-001〜026)の概要。本書はそのうち ONL-010 を実装レベルまで詳細化したもの。
 本書の目的：本書だけを見て、この処理のバックエンドを実装・単体テストできる粒度で記述する。</t>
         </is>
       </c>
@@ -787,7 +787,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:E29"/>
+  <dimension ref="A2:E32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -862,433 +862,469 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="49" customHeight="1">
+    <row r="5" ht="79" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
+          <t>E-003</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>対象日に出勤打刻がないため、休憩・離席を修正できません。／終了時刻は開始時刻より後の時刻を指定してください。／休憩・離席の時刻は出勤 HH:mm〜退勤 HH:mm の範囲内で指定してください。</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>休憩・離席修正の最終承認時の再検証（申請後に打刻が変わった等）。全体ロールバック</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>AttendanceService#checkBreakCorrection（ApprovalService#applyApproved 経由）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="49" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
           <t>E-004</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>409</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>休暇残日数が不足しています。</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>最終承認時、LIMITED 種別の休暇で残日数が申請日数に満たない（申請時の引当後に付与行の失効・他の申請の消化があった場合など）</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>LeaveBalanceService#consume（ApprovalService#applyApproved 経由）</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="19" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
+    <row r="7" ht="34" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>E-005</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>409</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>他の休憩・離席の時間帯と重なっています。</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>休憩・離席修正の最終承認時に他の区間と重なった。全体ロールバック</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>AttendanceService#checkBreakCorrection（同上）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="19" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>E-009</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>403</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>自分の申請は承認できません。</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>requests.user_id ＝ 実行者</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>ApprovalService#loadContext</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="64" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
+    <row r="9" ht="64" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>E-010</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>403</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>この操作を行う権限がありません。</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>ロール不足（JWT／DB）・INACTIVE・ステップが存在しない・自分の承認対象でない・承認者未設定（approver_id NULL）の1段目</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E9" s="7" t="inlineStr">
         <is>
           <t>@PreAuthorize→GlobalExceptionHandler#handleAccessDenied／ApprovalService#requireApprover／#loadContext</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="49" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
+    <row r="10" ht="49" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>E-011</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>409</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>この申請は既に処理されています。</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>step.status≠WAITING／request.status≠PENDING（取下げ・差戻し等）／current_step≠step_no／条件付き UPDATE が 0 件（競合）</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>ApprovalService#loadContext／#recordStep／#updateRequestStatus／#advanceToFinalStep</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
+    <row r="11" ht="49" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>E-012</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>500</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C11" s="7" t="inlineStr">
         <is>
           <t>システムエラーが発生しました。しばらくしてから再度お試しください。</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>上記以外の予期しない例外（corrected_clock が欠落、打刻の UNIQUE 違反、DB 接続断など）</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>上記以外の予期しない例外（corrected_clock が欠落、corrected_break_* が欠落、打刻の UNIQUE 違反、DB 接続断など）</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
         <is>
           <t>GlobalExceptionHandler#handleOther</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>8.2 ログ出力</t>
         </is>
       </c>
-      <c r="B11" s="9" t="n"/>
-      <c r="C11" s="9" t="n"/>
-      <c r="D11" s="9" t="n"/>
-      <c r="E11" s="10" t="n"/>
-    </row>
-    <row r="12" ht="19" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="B13" s="9" t="n"/>
+      <c r="C13" s="9" t="n"/>
+      <c r="D13" s="9" t="n"/>
+      <c r="E13" s="10" t="n"/>
+    </row>
+    <row r="14" ht="19" customHeight="1">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>レベル</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>タイミング</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>出力内容</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D14" s="6" t="inlineStr">
         <is>
           <t>出力禁止</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="E14" s="6" t="inlineStr">
         <is>
           <t>出力箇所</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="49" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
+    <row r="15" ht="49" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>承認の成功時</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
+      <c r="C15" s="7" t="inlineStr">
         <is>
           <t>approval processed: action=APPROVE, stepId, requestId, stepNo, actorId, requestStatus</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D15" s="7" t="inlineStr">
         <is>
           <t>コメント本文・申請理由・氏名</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
+      <c r="E15" s="7" t="inlineStr">
         <is>
           <t>ApprovalService#approve</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="49" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
+    <row r="16" ht="49" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>WARN</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>E-010（requireApprover 失敗）</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C16" s="7" t="inlineStr">
         <is>
           <t>approver check failed: userId</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D16" s="7" t="inlineStr">
         <is>
           <t>トークン</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="E16" s="7" t="inlineStr">
         <is>
           <t>ApprovalService#requireApprover</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="34" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
+    <row r="17" ht="34" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>WARN</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>E-009 自己承認の試行</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="C17" s="7" t="inlineStr">
         <is>
           <t>self approval attempt: stepId, actorId</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="D17" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
+      <c r="E17" s="7" t="inlineStr">
         <is>
           <t>ApprovalService#loadContext</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="34" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
+    <row r="18" ht="34" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>WARN</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>通知先の管理者がいない</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="C18" s="7" t="inlineStr">
         <is>
           <t>no active admin to notify: requestId</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D18" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
+      <c r="E18" s="7" t="inlineStr">
         <is>
           <t>ApprovalService#notifyApprovers</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="49" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>DEBUG</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>E-011（競合・処理済み）</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>already processed: stepId, actorId</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>ApprovalService#alreadyProcessed 呼出し元</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="64" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>残日数消化（LeaveBalanceService）</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>Leave consumed: userId, leaveTypeId, days, useDate（ONL-013 側で出力）</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>LeaveBalanceService#consume</t>
         </is>
       </c>
     </row>
     <row r="19" ht="49" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
         <is>
+          <t>DEBUG</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>E-011（競合・処理済み）</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>already processed: stepId, actorId</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>ApprovalService#alreadyProcessed 呼出し元</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="64" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>休憩・離席修正の反映（AttendanceService）</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>Break-correction applied: userId, workDate, kind（AttendanceService 側で出力）</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>AttendanceService#applyBreakCorrection</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="64" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>残日数消化（LeaveBalanceService）</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>Leave consumed: userId, leaveTypeId, days, useDate（ONL-013 側で出力）</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>LeaveBalanceService#consume</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="49" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
           <t>ERROR</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>予期しない例外（E-012）</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="C22" s="7" t="inlineStr">
         <is>
           <t>Unexpected error ＋スタックトレース</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr">
         <is>
           <t>トークン・コメント本文</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
+      <c r="E22" s="7" t="inlineStr">
         <is>
           <t>GlobalExceptionHandler</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="8" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>8.3 セキュリティ・権限上の考慮</t>
         </is>
       </c>
-      <c r="B21" s="9" t="n"/>
-      <c r="C21" s="9" t="n"/>
-      <c r="D21" s="9" t="n"/>
-      <c r="E21" s="10" t="n"/>
-    </row>
-    <row r="22" ht="49" customHeight="1">
-      <c r="A22" s="11" t="inlineStr">
-        <is>
-          <t>認可（二重チェック）</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>Controller の @PreAuthorize(hasAnyRole('MANAGER','ADMIN')) で入口を絞り、さらに ApprovalService#requireApprover で DB の users.role / status を再確認する。JWT の role は最大8時間古い可能性があるため、降格・無効化の直後でも操作できないようにする。SecurityConfig に @EnableMethodSecurity を付与する前提（ONL-009 で実施）。</t>
-        </is>
-      </c>
-      <c r="C22" s="9" t="n"/>
-      <c r="D22" s="9" t="n"/>
-      <c r="E22" s="10" t="n"/>
-    </row>
-    <row r="23" ht="34" customHeight="1">
-      <c r="A23" s="11" t="inlineStr">
-        <is>
-          <t>データ所有（IDOR 対策）</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>他人宛のステップ ID を指定しても処理できない（1段目は approver_id＝自分、2段目は ADMIN のみ）。存在しない ID と他人宛 ID はどちらも E-010 / 403 で区別せず、ID の存在を推測させない（ONL-007/008 と同方針）。</t>
-        </is>
-      </c>
-      <c r="C23" s="9" t="n"/>
-      <c r="D23" s="9" t="n"/>
-      <c r="E23" s="10" t="n"/>
-    </row>
-    <row r="24" ht="34" customHeight="1">
-      <c r="A24" s="11" t="inlineStr">
-        <is>
-          <t>自己承認の禁止</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>申請者本人は承認不可（E-009）。ADMIN が自分の申請を2段目で承認することも不可。他の管理者が処理する（管理者が1名のみの場合は処理できないため、運用で2名以上を確保する）。</t>
-        </is>
-      </c>
+      <c r="B24" s="9" t="n"/>
       <c r="C24" s="9" t="n"/>
       <c r="D24" s="9" t="n"/>
       <c r="E24" s="10" t="n"/>
     </row>
-    <row r="25" ht="64" customHeight="1">
+    <row r="25" ht="49" customHeight="1">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>排他制御・二重実行</t>
+          <t>認可（二重チェック）</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>requests 行を SELECT … FOR UPDATE で直列化し（取下げ ONL-008 と同一手順）、approval_steps.status='WAITING' と requests.status='PENDING' AND current_step の条件付き UPDATE で最終保証。ダブルクリック・複数管理者の同時操作・取下げとの同時操作は、片方のみ成功し他方は E-011。休暇の二重消化は最終承認が1回しか成功しないため発生しない（consume 自体も付与行を FOR UPDATE する）。ロック順序は requests → leave_balances / attendance_records（他処理と逆順にならない）。</t>
+          <t>Controller の @PreAuthorize(hasAnyRole('MANAGER','ADMIN')) で入口を絞り、さらに ApprovalService#requireApprover で DB の users.role / status を再確認する。JWT の role は最大 2 時間（トークン有効期間）古い可能性があるため、降格・無効化の直後でも操作できないようにする。SecurityConfig に @EnableMethodSecurity を付与する前提（ONL-009 で実施）。</t>
         </is>
       </c>
       <c r="C25" s="9" t="n"/>
@@ -1298,12 +1334,12 @@
     <row r="26" ht="34" customHeight="1">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t>トランザクション</t>
+          <t>データ所有（IDOR 対策）</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>ステップ更新・申請更新・消化／打刻反映・通知を1トランザクションにまとめ、途中失敗は全ロールバックする（例：残日数不足 E-004 ではステップも WAITING のまま）。</t>
+          <t>他人宛のステップ ID を指定しても処理できない（1段目は approver_id＝自分、2段目は ADMIN のみ）。存在しない ID と他人宛 ID はどちらも E-010 / 403 で区別せず、ID の存在を推測させない（ONL-007/008 と同方針）。</t>
         </is>
       </c>
       <c r="C26" s="9" t="n"/>
@@ -1313,27 +1349,27 @@
     <row r="27" ht="34" customHeight="1">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>タイムゾーン</t>
+          <t>自己承認の禁止</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>acted_at は Clock（Asia/Tokyo）の現在日時（秒未満切捨て）。打刻修正の corrected_clock_in/out は JST のローカル日時としてそのまま attendance_records に保存する。休暇の利用日 useDate は requests.start_date（日付のみでタイムゾーン影響なし）。</t>
+          <t>申請者本人は承認不可（E-009）。ADMIN が自分の申請を2段目で承認することも不可。他の管理者が処理する（管理者が1名のみの場合は処理できないため、運用で2名以上を確保する）。</t>
         </is>
       </c>
       <c r="C27" s="9" t="n"/>
       <c r="D27" s="9" t="n"/>
       <c r="E27" s="10" t="n"/>
     </row>
-    <row r="28" ht="34" customHeight="1">
+    <row r="28" ht="79" customHeight="1">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>入力値の扱い</t>
+          <t>排他制御・二重実行</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>コメントは SQL にバインドパラメータで渡す（SQL インジェクション対策）。HTML のエスケープは表示側（Vue のテキスト展開）で行い、API は保存時に加工しない。コメント・氏名はログに出さない。</t>
+          <t>requests 行を SELECT … FOR UPDATE で直列化し（取下げ ONL-008 と同一手順）、approval_steps.status='WAITING' と requests.status='PENDING' AND current_step の条件付き UPDATE で最終保証。ダブルクリック・複数管理者の同時操作・取下げとの同時操作は、片方のみ成功し他方は E-011。休暇の二重消化は最終承認が1回しか成功しないため発生しない（consume 自体も付与行を FOR UPDATE する）。ロック順序は requests → leave_balances / attendance_records（休憩・離席修正は attendance_records の行ロックで attendance_breaks への反映も直列化。打刻・休憩の同時操作 ONL-002/003/024/025 も同じ行をロックする）（他処理と逆順にならない）。</t>
         </is>
       </c>
       <c r="C28" s="9" t="n"/>
@@ -1343,31 +1379,76 @@
     <row r="29" ht="34" customHeight="1">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>既知の制約（今後）</t>
+          <t>トランザクション</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>承認・差戻し・却下の操作履歴を残す監査ログ、承認者の代理設定、1段目の上長が INACTIVE になった場合の代理承認、1名の管理者が全段を承認する運用の制限。有効な ADMIN がいない場合、2段目は誰も処理できない。</t>
+          <t>ステップ更新・申請更新・消化／打刻反映／休憩・離席反映・通知を1トランザクションにまとめ、途中失敗は全ロールバックする（例：残日数不足 E-004、休憩・離席修正の再検証エラー E-003 / E-005 ではステップも WAITING のまま）。</t>
         </is>
       </c>
       <c r="C29" s="9" t="n"/>
       <c r="D29" s="9" t="n"/>
       <c r="E29" s="10" t="n"/>
     </row>
+    <row r="30" ht="49" customHeight="1">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>タイムゾーン</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>acted_at は Clock（Asia/Tokyo）の現在日時（秒未満切捨て）。打刻修正の corrected_clock_in/out は JST のローカル日時としてそのまま attendance_records に保存する。休暇の利用日 useDate は requests.start_date（日付のみでタイムゾーン影響なし）。 休憩・離席修正の corrected_break_start/end も JST のローカル日時のまま attendance_breaks に保存する。</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="n"/>
+      <c r="D30" s="9" t="n"/>
+      <c r="E30" s="10" t="n"/>
+    </row>
+    <row r="31" ht="34" customHeight="1">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>入力値の扱い</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>コメントは SQL にバインドパラメータで渡す（SQL インジェクション対策）。HTML のエスケープは表示側（Vue のテキスト展開）で行い、API は保存時に加工しない。コメント・氏名はログに出さない。</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="n"/>
+      <c r="D31" s="9" t="n"/>
+      <c r="E31" s="10" t="n"/>
+    </row>
+    <row r="32" ht="34" customHeight="1">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>既知の制約（今後）</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>承認・差戻し・却下の操作履歴を残す監査ログ、承認者の代理設定、1段目の上長が INACTIVE になった場合の代理承認、1名の管理者が全段を承認する運用の制限。有効な ADMIN がいない場合、2段目は誰も処理できない。</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="n"/>
+      <c r="D32" s="9" t="n"/>
+      <c r="E32" s="10" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A21:E21"/>
-    <mergeCell ref="B23:E23"/>
+    <mergeCell ref="B31:E31"/>
     <mergeCell ref="B26:E26"/>
     <mergeCell ref="B27:E27"/>
+    <mergeCell ref="A24:E24"/>
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="B30:E30"/>
     <mergeCell ref="B29:E29"/>
     <mergeCell ref="B25:E25"/>
-    <mergeCell ref="B24:E24"/>
+    <mergeCell ref="A13:E13"/>
     <mergeCell ref="B28:E28"/>
-    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="B32:E32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1380,7 +1461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:E39"/>
+  <dimension ref="A2:E47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1836,121 +1917,160 @@
       </c>
       <c r="E19" s="7" t="inlineStr"/>
     </row>
-    <row r="21">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>9.2 結合テスト（@SpringBootTest + DB）</t>
-        </is>
-      </c>
-      <c r="B21" s="9" t="n"/>
-      <c r="C21" s="9" t="n"/>
-      <c r="D21" s="9" t="n"/>
-      <c r="E21" s="10" t="n"/>
+    <row r="20" ht="79" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>2段目：ADMIN が BREAK_CORRECTION を承認・進行中の BREAK 区間あり</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>attendanceService.applyBreakCorrection(userId, startDate, "BREAK", start, end) が 1 回。consume は呼ばれない。申請者へ「休憩・離席修正申請（対象日 …）が承認されました。」</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>1段目承認では呼ばれない</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="49" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>異常</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>BREAK_CORRECTION の最終承認で applyBreakCorrection が BusinessException(E-003) を投げる</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>E-003 / 400 がそのまま伝播。通知は呼ばれない（結合テストでは step は WAITING のまま）</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr"/>
     </row>
     <row r="22" ht="19" customHeight="1">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>No.</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>区分</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>観点・条件</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>期待結果</t>
-        </is>
-      </c>
-      <c r="E22" s="6" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="49" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>異常</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>同上で E-005（他区間と重複）</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>E-005 / 409 が伝播</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr"/>
+    </row>
+    <row r="23" ht="64" customHeight="1">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>1段目：BREAK_CORRECTION を MANAGER が承認</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>applyBreakCorrection は呼ばれない。current_step＝2、管理者へ「…休憩・離席修正申請（対象日 …）の最終承認をお願いします。」</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr"/>
+    </row>
+    <row r="24" ht="79" customHeight="1">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>2段目：打刻修正・その日に休憩・離席の区間あり</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>attendanceBreakRepository から取得した区間が Span として calculate に渡り、work/overtime に休憩・離席が反映される。新規打刻でも saveAndFlush 後の id で区間を検索</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>区間なしなら法定休憩（6h 超 45 分／8h 超 60 分）</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="34" customHeight="1">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
           <t>異常</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>同一ステップを2スレッドで同時に承認</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>片方 200、もう片方 E-011。leave_balances.used_days は1回分のみ加算、通知も1セット</t>
-        </is>
-      </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>排他制御の確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="49" customHeight="1">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>異常</t>
-        </is>
-      </c>
-      <c r="C24" s="7" t="inlineStr">
-        <is>
-          <t>承認と取下げ（ONL-008）の同時実行</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>結果が APPROVED と WITHDRAWN の混在にならない（先にロックを取った方のみ有効、他方は E-011）</t>
-        </is>
-      </c>
-      <c r="E24" s="7" t="inlineStr"/>
-    </row>
-    <row r="25" ht="49" customHeight="1">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>異常</t>
-        </is>
-      </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>最終承認で残日数不足(E-004)</t>
+          <t>BREAK_CORRECTION で corrected_break_kind が null（データ不整合）</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>approval_steps は WAITING のまま、requests は PENDING のまま、notifications は増えない（全ロールバック）</t>
-        </is>
-      </c>
-      <c r="E25" s="7" t="inlineStr"/>
+          <t>例外（API では E-012）</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>通常は申請時に必須チェック済み</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>9.3 ApprovalController（MockMvc / API テスト）</t>
+          <t>9.2 結合テスト（@SpringBootTest + DB）</t>
         </is>
       </c>
       <c r="B27" s="9" t="n"/>
@@ -1985,121 +2105,121 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="19" customHeight="1">
+    <row r="29" ht="49" customHeight="1">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
+          <t>異常</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>同一ステップを2スレッドで同時に承認</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>片方 200、もう片方 E-011。leave_balances.used_days は1回分のみ加算、通知も1セット</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>排他制御の確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="49" customHeight="1">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>異常</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>承認と取下げ（ONL-008）の同時実行</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>結果が APPROVED と WITHDRAWN の混在にならない（先にロックを取った方のみ有効、他方は E-011）</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr"/>
+    </row>
+    <row r="31" ht="49" customHeight="1">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>異常</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>最終承認で残日数不足(E-004)</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>approval_steps は WAITING のまま、requests は PENDING のまま、notifications は増えない（全ロールバック）</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr"/>
+    </row>
+    <row r="32" ht="79" customHeight="1">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
           <t>正常</t>
         </is>
       </c>
-      <c r="C29" s="7" t="inlineStr">
-        <is>
-          <t>MANAGER で body 省略</t>
-        </is>
-      </c>
-      <c r="D29" s="7" t="inlineStr">
-        <is>
-          <t>200 {requestStatus}</t>
-        </is>
-      </c>
-      <c r="E29" s="7" t="inlineStr"/>
-    </row>
-    <row r="30" ht="19" customHeight="1">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="inlineStr">
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>BREAK_CORRECTION：最終承認後の attendance_breaks（結合）</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>進行中の同種別区間があればその行の start_at/end_at が置換され、無ければ 1 行追加。退勤済みなら attendance_records.work_minutes / overtime_minutes が再計算される</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr"/>
+    </row>
+    <row r="33" ht="49" customHeight="1">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
         <is>
           <t>異常</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
-        <is>
-          <t>EMPLOYEE のトークン</t>
-        </is>
-      </c>
-      <c r="D30" s="7" t="inlineStr">
-        <is>
-          <t>403 E-010</t>
-        </is>
-      </c>
-      <c r="E30" s="7" t="inlineStr"/>
-    </row>
-    <row r="31" ht="34" customHeight="1">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>異常</t>
-        </is>
-      </c>
-      <c r="C31" s="7" t="inlineStr">
-        <is>
-          <t>トークンなし</t>
-        </is>
-      </c>
-      <c r="D31" s="7" t="inlineStr">
-        <is>
-          <t>401 / E-001（AuthenticationEntryPoint の JSON）</t>
-        </is>
-      </c>
-      <c r="E31" s="7" t="inlineStr"/>
-    </row>
-    <row r="32" ht="34" customHeight="1">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>異常</t>
-        </is>
-      </c>
-      <c r="C32" s="7" t="inlineStr">
-        <is>
-          <t>comment が501文字</t>
-        </is>
-      </c>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>400 E-002「コメントは500文字以内で入力してください。」</t>
-        </is>
-      </c>
-      <c r="E32" s="7" t="inlineStr">
-        <is>
-          <t>500文字は成功（境界値）</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="34" customHeight="1">
-      <c r="A33" s="7" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="B33" s="7" t="inlineStr">
-        <is>
-          <t>異常</t>
-        </is>
-      </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>パス {id} が数値でない</t>
+          <t>申請後に同時間帯の休憩が打刻されてから最終承認（結合）</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>400 E-002「入力内容が正しくありません。」</t>
+          <t>E-005 / 409。attendance_breaks・approval_steps・requests・notifications は全て変化なし（ロールバック）</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr"/>
@@ -2107,7 +2227,7 @@
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>9.4 通知の type / requestId（Mockito・結合）</t>
+          <t>9.3 ApprovalController（MockMvc / API テスト）</t>
         </is>
       </c>
       <c r="B35" s="9" t="n"/>
@@ -2142,10 +2262,10 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="49" customHeight="1">
+    <row r="37" ht="19" customHeight="1">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
@@ -2155,65 +2275,222 @@
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
+          <t>MANAGER で body 省略</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>200 {requestStatus}</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr"/>
+    </row>
+    <row r="38" ht="19" customHeight="1">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>異常</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>EMPLOYEE のトークン</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>403 E-010</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr"/>
+    </row>
+    <row r="39" ht="34" customHeight="1">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>異常</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>トークンなし</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>401 / E-001（AuthenticationEntryPoint の JSON）</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr"/>
+    </row>
+    <row r="40" ht="34" customHeight="1">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>異常</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>comment が501文字</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>400 E-002「コメントは500文字以内で入力してください。」</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>500文字は成功（境界値）</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="34" customHeight="1">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>異常</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>パス {id} が数値でない</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>400 E-002「入力内容が正しくありません。」</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>9.4 通知の type / requestId（Mockito・結合）</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="n"/>
+      <c r="C43" s="9" t="n"/>
+      <c r="D43" s="9" t="n"/>
+      <c r="E43" s="10" t="n"/>
+    </row>
+    <row r="44" ht="19" customHeight="1">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>観点・条件</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>期待結果</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="49" customHeight="1">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
           <t>1段目承認後の notifications を確認（結合）</t>
         </is>
       </c>
-      <c r="D37" s="7" t="inlineStr">
+      <c r="D45" s="7" t="inlineStr">
         <is>
           <t>申請者宛 type=REQUEST_APPROVED、各管理者宛 type=REQUEST_SUBMITTED。いずれも request_id＝申請ID、is_read=FALSE</t>
         </is>
       </c>
-      <c r="E37" s="7" t="inlineStr">
+      <c r="E45" s="7" t="inlineStr">
         <is>
           <t>旧種別名（STEP_APPROVED 等）が保存されない</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="49" customHeight="1">
-      <c r="A38" s="7" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="B38" s="7" t="inlineStr">
+    <row r="46" ht="49" customHeight="1">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
       </c>
-      <c r="C38" s="7" t="inlineStr">
+      <c r="C46" s="7" t="inlineStr">
         <is>
           <t>2段目承認後の notifications を確認（結合）</t>
         </is>
       </c>
-      <c r="D38" s="7" t="inlineStr">
+      <c r="D46" s="7" t="inlineStr">
         <is>
           <t>申請者宛 type=REQUEST_APPROVED（本文は『承認されました』）1件のみ。request_id＝申請ID</t>
         </is>
       </c>
-      <c r="E38" s="7" t="inlineStr"/>
-    </row>
-    <row r="39" ht="49" customHeight="1">
-      <c r="A39" s="7" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B39" s="7" t="inlineStr">
+      <c r="E46" s="7" t="inlineStr"/>
+    </row>
+    <row r="47" ht="49" customHeight="1">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
       </c>
-      <c r="C39" s="7" t="inlineStr">
+      <c r="C47" s="7" t="inlineStr">
         <is>
           <t>承認後の approval_steps.updated_at / requests.updated_at を確認（結合）</t>
         </is>
       </c>
-      <c r="D39" s="7" t="inlineStr">
+      <c r="D47" s="7" t="inlineStr">
         <is>
           <t>更新前より新しい（DB トリガで更新）。SQL にも Entity にも updated_at の設定はない</t>
         </is>
       </c>
-      <c r="E39" s="7" t="inlineStr">
+      <c r="E47" s="7" t="inlineStr">
         <is>
           <t>D2</t>
         </is>
@@ -2222,9 +2499,9 @@
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A35:E35"/>
     <mergeCell ref="A27:E27"/>
-    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A43:E43"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2237,7 +2514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2321,6 +2598,29 @@
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr"/>
+    </row>
+    <row r="4" ht="139" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Wang Sheng</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>休憩・離席修正申請（BREAK_CORRECTION）と打刻の休憩・離席に対応：最終承認で AttendanceService#applyBreakCorrection を呼び attendance_breaks へ反映（承認時にも E-003 / E-005 を再検証しロールバック）。打刻修正（CLOCK_CORRECTION）の反映は AttendanceRecord(userId, workDate) コンストラクタ・saveAndFlush・休憩区間（Span）込みの再計算に合わせて修正。ApprovalService の依存（AttendanceBreakRepository / AttendanceService）、describe、mapping（corrected_break_* / attendance_breaks）、SQL、エラー、テスト観点を追加。JWT 有効期間の記述を 2 時間に修正</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2334,7 +2634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:F44"/>
+  <dimension ref="A2:F48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2421,7 +2721,7 @@
       <c r="E6" s="9" t="n"/>
       <c r="F6" s="10" t="n"/>
     </row>
-    <row r="7" ht="49" customHeight="1">
+    <row r="7" ht="64" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
         <is>
           <t>目的</t>
@@ -2429,7 +2729,7 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>承認待ちの承認ステップ（approval_steps.id）を承認する。1段目（上長）の承認では申請を2段目（管理者）へ進め、2段目（管理者）の承認では申請を APPROVED で確定し、休暇なら休暇残日数の消化、打刻修正なら attendance_records への反映を行い、関係者へ通知を登録する。ApprovalService の共通処理（権限確認・状態確認・排他制御・通知）の定義元でもあり、ONL-011（差戻し）・ONL-012（却下）がこれを再利用する。</t>
+          <t>承認待ちの承認ステップ（approval_steps.id）を承認する。1段目（上長）の承認では申請を2段目（管理者）へ進め、2段目（管理者）の承認では申請を APPROVED で確定し、休暇なら休暇残日数の消化、打刻修正なら attendance_records への反映（休憩・離席の記録を考慮して再計算）、休憩・離席修正なら attendance_breaks への反映（AttendanceService#applyBreakCorrection）を行い、関係者へ通知を登録する。ApprovalService の共通処理（権限確認・状態確認・排他制御・通知）の定義元でもあり、ONL-011（差戻し）・ONL-012（却下）がこれを再利用する。</t>
         </is>
       </c>
       <c r="C7" s="9" t="n"/>
@@ -2469,7 +2769,7 @@
       <c r="E9" s="9" t="n"/>
       <c r="F9" s="10" t="n"/>
     </row>
-    <row r="10" ht="64" customHeight="1">
+    <row r="10" ht="94" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
         <is>
           <t>事後条件</t>
@@ -2478,8 +2778,8 @@
       <c r="B10" s="7" t="inlineStr">
         <is>
           <t>【1段目】approval_steps(1)＝APPROVED、requests.current_step＝2（status は PENDING のまま）、申請者と有効な全管理者へ通知。
-【2段目】approval_steps(2)＝APPROVED（approver_id＝実行した管理者）、requests.status＝APPROVED、休暇は leave_balances.used_days 加算／打刻修正は attendance_records 更新、申請者へ通知。
-【失敗時】いずれかで例外になった場合は全更新をロールバック（部分更新を残さない）。</t>
+【2段目】approval_steps(2)＝APPROVED（approver_id＝実行した管理者）、requests.status＝APPROVED、休暇は leave_balances.used_days 加算／打刻修正は attendance_records 更新（その日の attendance_breaks を反映して勤務・残業を再計算）／休憩・離席修正は attendance_breaks の該当区間を更新または追加（退勤済みなら勤務・残業を再計算）、申請者へ通知。
+【失敗時】いずれかで例外になった場合は全更新をロールバック（部分更新を残さない）。休憩・離席修正は最終承認時にも対象日の打刻と他区間との重なりを再検証し、不整合なら E-003（400）／E-005（409）でロールバックする（ステップは WAITING のまま）。</t>
         </is>
       </c>
       <c r="C10" s="9" t="n"/>
@@ -2495,7 +2795,7 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>approval_steps: R/U, requests: R/U, users: R, leave_balances: R/U（LeaveBalanceService 経由）, attendance_records: C/R/U, notifications: C（NotificationService 経由）</t>
+          <t>approval_steps: R/U, requests: R/U, users: R, leave_balances: R/U（LeaveBalanceService 経由）, attendance_records: C/R/U, attendance_breaks: R/C/U, notifications: C（NotificationService 経由）</t>
         </is>
       </c>
       <c r="C11" s="9" t="n"/>
@@ -2511,7 +2811,7 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>ApprovalService#approve に @Transactional（1 リクエスト＝1 トランザクション。READ COMMITTED）。ステップ更新・申請更新・残日数消化／打刻反映・通知登録をすべて同一トランザクションで実行し、BusinessException（RuntimeException）の throw で全体をロールバックする。排他は「requests 行の SELECT ... FOR UPDATE（RequestRepository#findByIdForUpdate。ONL-008 取下げと同じ手順）」と「状態条件付き UPDATE」（WHERE status='WAITING' 等）の二重で行う。</t>
+          <t>ApprovalService#approve に @Transactional（1 リクエスト＝1 トランザクション。READ COMMITTED）。ステップ更新・申請更新・残日数消化／打刻反映／休憩・離席反映・通知登録をすべて同一トランザクションで実行し、BusinessException（RuntimeException）の throw で全体をロールバックする。排他は「requests 行の SELECT ... FOR UPDATE（RequestRepository#findByIdForUpdate。ONL-008 取下げと同じ手順）」と「状態条件付き UPDATE」（WHERE status='WAITING' 等）の二重で行う。</t>
         </is>
       </c>
       <c r="C12" s="9" t="n"/>
@@ -2584,7 +2884,7 @@
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>E-002 / E-004 / E-009 / E-010 / E-011 / E-012、I-004（承認しました。）</t>
+          <t>E-002 / E-003 / E-004 / E-005 / E-009 / E-010 / E-011 / E-012、I-004（承認しました。）</t>
         </is>
       </c>
       <c r="D17" s="9" t="n"/>
@@ -2704,7 +3004,7 @@
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>approval_steps / requests / leave_balances / attendance_records / notifications</t>
+          <t>approval_steps / requests / leave_balances / attendance_records / attendance_breaks / notifications</t>
         </is>
       </c>
       <c r="D23" s="9" t="n"/>
@@ -2751,570 +3051,673 @@
       <c r="E25" s="9" t="n"/>
       <c r="F25" s="10" t="n"/>
     </row>
-    <row r="27">
-      <c r="A27" s="8" t="inlineStr">
-        <is>
-          <t>1.3 対象クラス一覧（パッケージ：com.example.kintaiflow）</t>
-        </is>
-      </c>
-      <c r="B27" s="9" t="n"/>
-      <c r="C27" s="9" t="n"/>
+    <row r="26" ht="34" customHeight="1">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>ONL-005</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>申請作成</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>AttendanceService#validateBreakCorrection / checkBreakCorrection（休憩・離席修正の検証。申請時と最終承認時で共用）の定義元</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="n"/>
+      <c r="E26" s="9" t="n"/>
+      <c r="F26" s="10" t="n"/>
+    </row>
+    <row r="27" ht="19" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>ONL-024 / ONL-025</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>休憩・離席開始／終了</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>attendance_breaks・AttendanceBreak エンティティ・部分ユニーク索引 uq_attendance_breaks_open の定義元</t>
+        </is>
+      </c>
       <c r="D27" s="9" t="n"/>
       <c r="E27" s="9" t="n"/>
       <c r="F27" s="10" t="n"/>
     </row>
-    <row r="28" ht="19" customHeight="1">
-      <c r="A28" s="6" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>1.3 対象クラス一覧（パッケージ：com.example.kintaiflow）</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="n"/>
+      <c r="C29" s="9" t="n"/>
+      <c r="D29" s="9" t="n"/>
+      <c r="E29" s="9" t="n"/>
+      <c r="F29" s="10" t="n"/>
+    </row>
+    <row r="30" ht="19" customHeight="1">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>パッケージ</t>
         </is>
       </c>
-      <c r="B28" s="6" t="inlineStr">
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>クラス名</t>
         </is>
       </c>
-      <c r="C28" s="6" t="inlineStr">
+      <c r="C30" s="6" t="inlineStr">
         <is>
           <t>種別</t>
         </is>
       </c>
-      <c r="D28" s="6" t="inlineStr">
+      <c r="D30" s="6" t="inlineStr">
         <is>
           <t>責務</t>
         </is>
       </c>
-      <c r="E28" s="6" t="inlineStr">
+      <c r="E30" s="6" t="inlineStr">
         <is>
           <t>ファイル</t>
         </is>
       </c>
-      <c r="F28" s="6" t="inlineStr">
+      <c r="F30" s="6" t="inlineStr">
         <is>
           <t>新規/既存</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="64" customHeight="1">
-      <c r="A29" s="7" t="inlineStr">
-        <is>
-          <t>controller</t>
-        </is>
-      </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>ApprovalController</t>
-        </is>
-      </c>
-      <c r="C29" s="7" t="inlineStr">
-        <is>
-          <t>Controller</t>
-        </is>
-      </c>
-      <c r="D29" s="7" t="inlineStr">
-        <is>
-          <t>承認系 API の入口（API-009〜012）。本処理で approve を追記（クラスは先に着手した処理が新規作成）</t>
-        </is>
-      </c>
-      <c r="E29" s="7" t="inlineStr">
-        <is>
-          <t>controller/ApprovalController.java</t>
-        </is>
-      </c>
-      <c r="F29" s="7" t="inlineStr">
-        <is>
-          <t>追記（新規は ONL-009）</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="49" customHeight="1">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>service</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>ApprovalService</t>
-        </is>
-      </c>
-      <c r="C30" s="7" t="inlineStr">
-        <is>
-          <t>Service</t>
-        </is>
-      </c>
-      <c r="D30" s="7" t="inlineStr">
-        <is>
-          <t>承認・差戻し・却下の業務ロジックと共通処理。本処理でクラス本体・共通メソッドを新規定義</t>
-        </is>
-      </c>
-      <c r="E30" s="7" t="inlineStr">
-        <is>
-          <t>service/ApprovalService.java</t>
-        </is>
-      </c>
-      <c r="F30" s="7" t="inlineStr">
-        <is>
-          <t>新規（ONL-009/011/012 が追記）</t>
         </is>
       </c>
     </row>
     <row r="31" ht="64" customHeight="1">
       <c r="A31" s="7" t="inlineStr">
         <is>
+          <t>controller</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>ApprovalController</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>Controller</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>承認系 API の入口（API-009〜012）。本処理で approve を追記（クラスは先に着手した処理が新規作成）</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>controller/ApprovalController.java</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>追記（新規は ONL-009）</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="49" customHeight="1">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>ApprovalService</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>承認・差戻し・却下の業務ロジックと共通処理。本処理でクラス本体・共通メソッドを新規定義</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>service/ApprovalService.java</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>新規（ONL-009/011/012 が追記）</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="64" customHeight="1">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
           <t>repository</t>
         </is>
       </c>
-      <c r="B31" s="7" t="inlineStr">
+      <c r="B33" s="7" t="inlineStr">
         <is>
           <t>ApprovalStepRepository</t>
         </is>
       </c>
-      <c r="C31" s="7" t="inlineStr">
+      <c r="C33" s="7" t="inlineStr">
         <is>
           <t>Repository</t>
         </is>
       </c>
-      <c r="D31" s="7" t="inlineStr">
+      <c r="D33" s="7" t="inlineStr">
         <is>
           <t>承認ステップ。actIfWaiting（条件付き UPDATE）を追加。findById / findByRequestIdOrderByStepNo は既存を使用</t>
         </is>
       </c>
-      <c r="E31" s="7" t="inlineStr">
+      <c r="E33" s="7" t="inlineStr">
         <is>
           <t>repository/ApprovalStepRepository.java</t>
         </is>
       </c>
-      <c r="F31" s="7" t="inlineStr">
+      <c r="F33" s="7" t="inlineStr">
         <is>
           <t>追記（新規は ONL-005）</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="79" customHeight="1">
-      <c r="A32" s="7" t="inlineStr">
+    <row r="34" ht="79" customHeight="1">
+      <c r="A34" s="7" t="inlineStr">
         <is>
           <t>repository</t>
         </is>
       </c>
-      <c r="B32" s="7" t="inlineStr">
+      <c r="B34" s="7" t="inlineStr">
         <is>
           <t>RequestRepository</t>
         </is>
       </c>
-      <c r="C32" s="7" t="inlineStr">
+      <c r="C34" s="7" t="inlineStr">
         <is>
           <t>Repository</t>
         </is>
       </c>
-      <c r="D32" s="7" t="inlineStr">
+      <c r="D34" s="7" t="inlineStr">
         <is>
           <t>申請。updateStatusIfPending / advanceStepIfPending（条件付き UPDATE）を追加。findByIdForUpdate（行ロック）は既存を使用</t>
         </is>
       </c>
-      <c r="E32" s="7" t="inlineStr">
+      <c r="E34" s="7" t="inlineStr">
         <is>
           <t>repository/RequestRepository.java</t>
         </is>
       </c>
-      <c r="F32" s="7" t="inlineStr">
+      <c r="F34" s="7" t="inlineStr">
         <is>
           <t>追記（新規は ONL-005）</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="34" customHeight="1">
-      <c r="A33" s="7" t="inlineStr">
+    <row r="35" ht="34" customHeight="1">
+      <c r="A35" s="7" t="inlineStr">
         <is>
           <t>repository</t>
         </is>
       </c>
-      <c r="B33" s="7" t="inlineStr">
+      <c r="B35" s="7" t="inlineStr">
         <is>
           <t>UserRepository</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
+      <c r="C35" s="7" t="inlineStr">
         <is>
           <t>Repository</t>
         </is>
       </c>
-      <c r="D33" s="7" t="inlineStr">
+      <c r="D35" s="7" t="inlineStr">
         <is>
           <t>実行者・申請者の取得（findById）</t>
         </is>
       </c>
-      <c r="E33" s="7" t="inlineStr">
+      <c r="E35" s="7" t="inlineStr">
         <is>
           <t>repository/UserRepository.java</t>
         </is>
       </c>
-      <c r="F33" s="7" t="inlineStr">
+      <c r="F35" s="7" t="inlineStr">
         <is>
           <t>既存（ONL-001）</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="49" customHeight="1">
-      <c r="A34" s="7" t="inlineStr">
-        <is>
-          <t>repository</t>
-        </is>
-      </c>
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>AttendanceRecordRepository</t>
-        </is>
-      </c>
-      <c r="C34" s="7" t="inlineStr">
-        <is>
-          <t>Repository</t>
-        </is>
-      </c>
-      <c r="D34" s="7" t="inlineStr">
-        <is>
-          <t>打刻の行ロック付き取得 findWithLockByUserIdAndWorkDate / save</t>
-        </is>
-      </c>
-      <c r="E34" s="7" t="inlineStr">
-        <is>
-          <t>repository/AttendanceRecordRepository.java</t>
-        </is>
-      </c>
-      <c r="F34" s="7" t="inlineStr">
-        <is>
-          <t>既存（ONL-002）</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="49" customHeight="1">
-      <c r="A35" s="7" t="inlineStr">
-        <is>
-          <t>service</t>
-        </is>
-      </c>
-      <c r="B35" s="7" t="inlineStr">
-        <is>
-          <t>ApprovalRouteService</t>
-        </is>
-      </c>
-      <c r="C35" s="7" t="inlineStr">
-        <is>
-          <t>Service</t>
-        </is>
-      </c>
-      <c r="D35" s="7" t="inlineStr">
-        <is>
-          <t>2段目承認の通知先（有効な全管理者・申請者除く）の解決 resolveCurrentApproverIds</t>
-        </is>
-      </c>
-      <c r="E35" s="7" t="inlineStr">
-        <is>
-          <t>service/ApprovalRouteService.java</t>
-        </is>
-      </c>
-      <c r="F35" s="7" t="inlineStr">
-        <is>
-          <t>既存（ONL-005）</t>
         </is>
       </c>
     </row>
     <row r="36" ht="49" customHeight="1">
       <c r="A36" s="7" t="inlineStr">
         <is>
+          <t>repository</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>AttendanceRecordRepository</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>Repository</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>打刻の行ロック付き取得 findWithLockByUserIdAndWorkDate / saveAndFlush / save</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>repository/AttendanceRecordRepository.java</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>既存（ONL-002）</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="64" customHeight="1">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>repository</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>AttendanceBreakRepository</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>Repository</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>打刻の休憩・離席区間の取得 findByAttendanceRecordIdOrderByStartAtAsc（打刻修正の再計算用）</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>repository/AttendanceBreakRepository.java</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>既存（ONL-024）</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="79" customHeight="1">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
           <t>service</t>
         </is>
       </c>
-      <c r="B36" s="7" t="inlineStr">
-        <is>
-          <t>LeaveBalanceService</t>
-        </is>
-      </c>
-      <c r="C36" s="7" t="inlineStr">
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>AttendanceService</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
         <is>
           <t>Service</t>
         </is>
       </c>
-      <c r="D36" s="7" t="inlineStr">
-        <is>
-          <t>休暇残日数の消化 consume（FIFO。UNLIMITED は内部でスキップ）</t>
-        </is>
-      </c>
-      <c r="E36" s="7" t="inlineStr">
-        <is>
-          <t>service/LeaveBalanceService.java</t>
-        </is>
-      </c>
-      <c r="F36" s="7" t="inlineStr">
-        <is>
-          <t>既存（ONL-013）</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="34" customHeight="1">
-      <c r="A37" s="7" t="inlineStr">
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>最終承認で休憩・離席修正を反映する applyBreakCorrection（検証 checkBreakCorrection・勤務時間再計算を含む。@Transactional）</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>service/AttendanceService.java</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t>既存（ONL-002/003/024/025。applyBreakCorrection は ONL-005 の検証と共用）</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="49" customHeight="1">
+      <c r="A39" s="7" t="inlineStr">
         <is>
           <t>service</t>
         </is>
       </c>
-      <c r="B37" s="7" t="inlineStr">
-        <is>
-          <t>AttendanceCalculator</t>
-        </is>
-      </c>
-      <c r="C37" s="7" t="inlineStr">
-        <is>
-          <t>Component</t>
-        </is>
-      </c>
-      <c r="D37" s="7" t="inlineStr">
-        <is>
-          <t>勤務時間・残業時間の計算 calculate</t>
-        </is>
-      </c>
-      <c r="E37" s="7" t="inlineStr">
-        <is>
-          <t>service/AttendanceCalculator.java</t>
-        </is>
-      </c>
-      <c r="F37" s="7" t="inlineStr">
-        <is>
-          <t>既存（ONL-003）</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="34" customHeight="1">
-      <c r="A38" s="7" t="inlineStr">
-        <is>
-          <t>service</t>
-        </is>
-      </c>
-      <c r="B38" s="7" t="inlineStr">
-        <is>
-          <t>NotificationService</t>
-        </is>
-      </c>
-      <c r="C38" s="7" t="inlineStr">
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>ApprovalRouteService</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
         <is>
           <t>Service</t>
         </is>
       </c>
-      <c r="D38" s="7" t="inlineStr">
-        <is>
-          <t>通知の登録 notify</t>
-        </is>
-      </c>
-      <c r="E38" s="7" t="inlineStr">
-        <is>
-          <t>service/NotificationService.java</t>
-        </is>
-      </c>
-      <c r="F38" s="7" t="inlineStr">
-        <is>
-          <t>既存（ONL-005 が定義元）</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="34" customHeight="1">
-      <c r="A39" s="7" t="inlineStr">
-        <is>
-          <t>entity</t>
-        </is>
-      </c>
-      <c r="B39" s="7" t="inlineStr">
-        <is>
-          <t>ApprovalStep / Request / User / AttendanceRecord</t>
-        </is>
-      </c>
-      <c r="C39" s="7" t="inlineStr">
-        <is>
-          <t>Entity</t>
-        </is>
-      </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>各テーブルのマッピング（本処理では新規作成しない）</t>
+          <t>2段目承認の通知先（有効な全管理者・申請者除く）の解決 resolveCurrentApproverIds</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>entity/*.java</t>
+          <t>service/ApprovalRouteService.java</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>既存</t>
+          <t>既存（ONL-005）</t>
         </is>
       </c>
     </row>
     <row r="40" ht="49" customHeight="1">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>entity</t>
+          <t>service</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>RequestType / RequestStatus / StepStatus</t>
+          <t>LeaveBalanceService</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>定数クラス</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>KF-BD-005 のコード値（String 定数）。本処理も同じ定数を使う</t>
+          <t>休暇残日数の消化 consume（FIFO。UNLIMITED は内部でスキップ）</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>entity/RequestType.java ほか</t>
+          <t>service/LeaveBalanceService.java</t>
         </is>
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>既存（ONL-005）</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="34" customHeight="1">
+          <t>既存（ONL-013）</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="49" customHeight="1">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>config</t>
+          <t>service</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>ClockConfig / AppTime</t>
+          <t>AttendanceCalculator</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>Configuration / Utility</t>
+          <t>Component</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>Clock Bean（Asia/Tokyo）と日時ユーティリティ</t>
+          <t>勤務時間・残業時間の計算 calculate(in, out, spans)（休憩・離席の区間を考慮。ONL-003）</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>config/ClockConfig.java ほか</t>
+          <t>service/AttendanceCalculator.java</t>
         </is>
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>既存（ONL-002）</t>
+          <t>既存（ONL-003）</t>
         </is>
       </c>
     </row>
     <row r="42" ht="34" customHeight="1">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>dto</t>
+          <t>service</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>ApprovalCommentRequest</t>
+          <t>NotificationService</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>DTO(record)</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>リクエスト（comment）＋入力チェック。ONL-011/012 も共用</t>
+          <t>通知の登録 notify</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>dto/ApprovalCommentRequest.java</t>
+          <t>service/NotificationService.java</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>新規</t>
+          <t>既存（ONL-005 が定義元）</t>
         </is>
       </c>
     </row>
     <row r="43" ht="34" customHeight="1">
       <c r="A43" s="7" t="inlineStr">
         <is>
+          <t>entity</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>ApprovalStep / Request / User / AttendanceRecord</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>Entity</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>各テーブルのマッピング（本処理では新規作成しない）</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>entity/*.java</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>既存</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="49" customHeight="1">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>entity</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>RequestType / RequestStatus / StepStatus</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>定数クラス</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>KF-BD-005 のコード値（String 定数）。本処理も同じ定数を使う</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>entity/RequestType.java ほか</t>
+        </is>
+      </c>
+      <c r="F44" s="7" t="inlineStr">
+        <is>
+          <t>既存（ONL-005）</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="34" customHeight="1">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>config</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>ClockConfig / AppTime</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>Configuration / Utility</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>Clock Bean（Asia/Tokyo）と日時ユーティリティ</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>config/ClockConfig.java ほか</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>既存（ONL-002）</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="34" customHeight="1">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
           <t>dto</t>
         </is>
       </c>
-      <c r="B43" s="7" t="inlineStr">
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>ApprovalCommentRequest</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>DTO(record)</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>リクエスト（comment）＋入力チェック。ONL-011/012 も共用</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>dto/ApprovalCommentRequest.java</t>
+        </is>
+      </c>
+      <c r="F46" s="7" t="inlineStr">
+        <is>
+          <t>新規</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="34" customHeight="1">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>dto</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
         <is>
           <t>ApprovalResultResponse</t>
         </is>
       </c>
-      <c r="C43" s="7" t="inlineStr">
+      <c r="C47" s="7" t="inlineStr">
         <is>
           <t>DTO(record)</t>
         </is>
       </c>
-      <c r="D43" s="7" t="inlineStr">
+      <c r="D47" s="7" t="inlineStr">
         <is>
           <t>正常応答（requestStatus）。ONL-011/012 も共用</t>
         </is>
       </c>
-      <c r="E43" s="7" t="inlineStr">
+      <c r="E47" s="7" t="inlineStr">
         <is>
           <t>dto/ApprovalResultResponse.java</t>
         </is>
       </c>
-      <c r="F43" s="7" t="inlineStr">
+      <c r="F47" s="7" t="inlineStr">
         <is>
           <t>新規</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="64" customHeight="1">
-      <c r="A44" s="7" t="inlineStr">
+    <row r="48" ht="64" customHeight="1">
+      <c r="A48" s="7" t="inlineStr">
         <is>
           <t>exception</t>
         </is>
       </c>
-      <c r="B44" s="7" t="inlineStr">
+      <c r="B48" s="7" t="inlineStr">
         <is>
           <t>BusinessException / GlobalExceptionHandler</t>
         </is>
       </c>
-      <c r="C44" s="7" t="inlineStr">
+      <c r="C48" s="7" t="inlineStr">
         <is>
           <t>Exception / ControllerAdvice</t>
         </is>
       </c>
-      <c r="D44" s="7" t="inlineStr">
+      <c r="D48" s="7" t="inlineStr">
         <is>
           <t>業務エラーの伝播と共通エラー応答（handleAccessDenied の追加は ONL-009、handleTypeMismatch は ONL-007）</t>
         </is>
       </c>
-      <c r="E44" s="7" t="inlineStr">
+      <c r="E48" s="7" t="inlineStr">
         <is>
           <t>exception/*.java</t>
         </is>
       </c>
-      <c r="F44" s="7" t="inlineStr">
+      <c r="F48" s="7" t="inlineStr">
         <is>
           <t>既存</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="24">
+  <mergeCells count="26">
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="C17:F17"/>
     <mergeCell ref="C23:F23"/>
     <mergeCell ref="B3:F3"/>
-    <mergeCell ref="A27:F27"/>
     <mergeCell ref="C19:F19"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="C18:F18"/>
@@ -3324,8 +3727,10 @@
     <mergeCell ref="C15:F15"/>
     <mergeCell ref="B8:F8"/>
     <mergeCell ref="C24:F24"/>
+    <mergeCell ref="A29:F29"/>
     <mergeCell ref="B10:F10"/>
     <mergeCell ref="C20:F20"/>
+    <mergeCell ref="C26:F26"/>
     <mergeCell ref="C16:F16"/>
     <mergeCell ref="C25:F25"/>
     <mergeCell ref="B9:F9"/>
@@ -3333,6 +3738,7 @@
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C27:F27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4138,7 +4544,7 @@
       <c r="E13" s="9" t="n"/>
       <c r="F13" s="10" t="n"/>
     </row>
-    <row r="14" ht="64" customHeight="1">
+    <row r="14" ht="79" customHeight="1">
       <c r="A14" s="7" t="inlineStr">
         <is>
           <t>⑪</t>
@@ -4152,7 +4558,7 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>2段目かつ LEAVE のみ LeaveBalanceService#consume(userId, leaveTypeId, days, startDate)。UNLIMITED 種別は consume 内でスキップされる。対象外（1段目・打刻修正）は常に Yes</t>
+          <t>2段目かつ LEAVE のみ LeaveBalanceService#consume(userId, leaveTypeId, days, startDate)。UNLIMITED 種別は consume 内でスキップされる。対象外（1段目・打刻修正）は常に Yes（休憩・離席修正は残日数に関係しないため対象外＝常に Yes）</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
@@ -4163,7 +4569,7 @@
       <c r="E14" s="9" t="n"/>
       <c r="F14" s="10" t="n"/>
     </row>
-    <row r="15" ht="64" customHeight="1">
+    <row r="15" ht="199" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
         <is>
           <t>⑫</t>
@@ -4171,13 +4577,15 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>最終承認の打刻修正は
-attendance_records へ反映</t>
+          <t>最終承認の打刻修正／休憩・離席修正を
+attendance へ反映</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2段目かつ CLOCK_CORRECTION のみ。(user_id, start_date) の打刻を行ロック付きで取得（無ければ新規）し、clock_in/out と AttendanceCalculator#calculate の結果を保存。対象外はスキップ</t>
+          <t>2段目かつ CLOCK_CORRECTION：(user_id, start_date) の打刻を行ロック付きで取得（無ければ新規）し、clock_in/out を設定して saveAndFlush、その日の attendance_breaks を取得して AttendanceCalculator#calculate(in, out, spans) の結果を保存。
+2段目かつ BREAK_CORRECTION：AttendanceService#applyBreakCorrection(userId, 対象日, 種別, 開始, 終了)。打刻を行ロック付きで取得して再検証（E-003 / E-005。ロールバック）→ 進行中の同種別区間があれば開始・終了を置換、無ければ INSERT → 退勤済みなら勤務・残業を再計算。
+LEAVE は対象外（スキップ）</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
@@ -4281,7 +4689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:F222"/>
+  <dimension ref="A2:F225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4719,7 +5127,7 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>BusinessException E-010(403) / E-009(403) / E-011(409) / E-004(409)
+          <t>BusinessException E-010(403) / E-009(403) / E-011(409) / E-004(409) / E-003(400)・E-005(409)（休憩・離席修正の最終承認時の再検証）
 その他の例外は E-012 / 500</t>
         </is>
       </c>
@@ -4728,7 +5136,7 @@
       <c r="E27" s="9" t="n"/>
       <c r="F27" s="10" t="n"/>
     </row>
-    <row r="28" ht="319" customHeight="1">
+    <row r="28" ht="334" customHeight="1">
       <c r="A28" s="11" t="inlineStr">
         <is>
           <t>処理詳細</t>
@@ -4750,7 +5158,7 @@
     result = RequestStatus.PENDING;
 } else {                                                             // ── 2段目（管理者＝最終承認）
     updateRequestStatus(ctx, RequestStatus.APPROVED);           // ⑨⑩ status→APPROVED（0件 → E-011）
-    applyApproved(req);                                              // ⑪⑫ 休暇: 残日数消化 / 打刻修正: 打刻更新
+    applyApproved(req);                                              // ⑪⑫ 休暇: 残日数消化 / 打刻修正: 打刻更新 / 休憩・離席修正: 区間の反映
     notifyApplicant(req, NotificationType.REQUEST_APPROVED, describe(req) + "が承認されました。");   // ⑬
     result = RequestStatus.APPROVED;
 }
@@ -4780,7 +5188,7 @@
       <c r="E29" s="9" t="n"/>
       <c r="F29" s="10" t="n"/>
     </row>
-    <row r="30" ht="64" customHeight="1">
+    <row r="30" ht="94" customHeight="1">
       <c r="A30" s="11" t="inlineStr">
         <is>
           <t>備考</t>
@@ -4788,7 +5196,8 @@
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>定数は entity パッケージの RequestStatus / StepStatus / RequestType と ApprovalRouteService.STEP_MANAGER(1) / STEP_ADMIN(2)（ONL-005）を使う。
+          <t>休憩・離席修正（BREAK_CORRECTION）の最終承認で検証エラーになった場合も BusinessException が伝播し、全体ロールバック（step・request は元のまま）。
+定数は entity パッケージの RequestStatus / StepStatus / RequestType と ApprovalRouteService.STEP_MANAGER(1) / STEP_ADMIN(2)（ONL-005）を使う。
 一度でも recordStep が成功した後に例外が発生した場合は、トランザクション全体がロールバックされるため step は WAITING のまま残る。
 通知登録も同一トランザクション内（通知の失敗は承認全体の失敗。NotificationService は REQUIRED で参加）。</t>
         </is>
@@ -4981,7 +5390,7 @@
       <c r="E42" s="9" t="n"/>
       <c r="F42" s="10" t="n"/>
     </row>
-    <row r="43" ht="34" customHeight="1">
+    <row r="43" ht="49" customHeight="1">
       <c r="A43" s="11" t="inlineStr">
         <is>
           <t>備考</t>
@@ -4989,7 +5398,7 @@
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>JWT の role claim は最大8時間古い可能性がある（異動・無効化の直後）。ロールの最終判断は DB の users.role/status で行う。
+          <t>JWT の role claim は最大 2 時間（トークン有効期間）古い可能性がある（異動・無効化の直後）。ロールの最終判断は DB の users.role/status で行う。
 失敗時は log.warn("approver check failed: userId={}", userId) を出力する。</t>
         </is>
       </c>
@@ -5970,7 +6379,7 @@
       <c r="E105" s="9" t="n"/>
       <c r="F105" s="10" t="n"/>
     </row>
-    <row r="106" ht="19" customHeight="1">
+    <row r="106" ht="34" customHeight="1">
       <c r="A106" s="11" t="inlineStr">
         <is>
           <t>説明</t>
@@ -5978,7 +6387,7 @@
       </c>
       <c r="B106" s="7" t="inlineStr">
         <is>
-          <t>最終承認（2段目）の副作用。休暇なら休暇残日数の消化、打刻修正なら attendance_records への反映を行う。</t>
+          <t>最終承認（2段目）の副作用。休暇なら休暇残日数の消化、打刻修正なら attendance_records への反映、休憩・離席修正なら attendance_breaks への反映を行う。</t>
         </is>
       </c>
       <c r="C106" s="9" t="n"/>
@@ -6058,7 +6467,7 @@
       <c r="E110" s="9" t="n"/>
       <c r="F110" s="10" t="n"/>
     </row>
-    <row r="111" ht="34" customHeight="1">
+    <row r="111" ht="49" customHeight="1">
       <c r="A111" s="11" t="inlineStr">
         <is>
           <t>例外</t>
@@ -6067,6 +6476,7 @@
       <c r="B111" s="7" t="inlineStr">
         <is>
           <t>BusinessException E-004 / 409（consume が残日数不足を検出）
+BusinessException E-003 / 400・E-005 / 409（休憩・離席修正の再検証。AttendanceService#applyBreakCorrection）
 IllegalStateException（必須項目欠落＝データ不整合。E-012 になる）</t>
         </is>
       </c>
@@ -6075,7 +6485,7 @@
       <c r="E111" s="9" t="n"/>
       <c r="F111" s="10" t="n"/>
     </row>
-    <row r="112" ht="94" customHeight="1">
+    <row r="112" ht="154" customHeight="1">
       <c r="A112" s="11" t="inlineStr">
         <is>
           <t>処理詳細</t>
@@ -6088,6 +6498,10 @@
     leaveBalanceService.consume(req.getUserId(), req.getLeaveTypeId(), req.getDays(), req.getStartDate());
 } else if (RequestType.CLOCK_CORRECTION.equals(req.getRequestType())) {
     applyClockCorrection(req);
+} else if (RequestType.BREAK_CORRECTION.equals(req.getRequestType())) {
+    // 検証（出勤打刻あり／開始&lt;終了／出退勤の範囲内／他区間と重ならない）→ 反映 → 退勤済みなら再計算。同一トランザクションで実行
+    attendanceService.applyBreakCorrection(req.getUserId(), req.getStartDate(), req.getCorrectedBreakKind(),
+            req.getCorrectedBreakStart(), req.getCorrectedBreakEnd());
 }</t>
         </is>
       </c>
@@ -6104,7 +6518,7 @@
       </c>
       <c r="B113" s="7" t="inlineStr">
         <is>
-          <t>LeaveBalanceService#consume / applyClockCorrection</t>
+          <t>LeaveBalanceService#consume / applyClockCorrection / AttendanceService#applyBreakCorrection</t>
         </is>
       </c>
       <c r="C113" s="9" t="n"/>
@@ -6112,7 +6526,7 @@
       <c r="E113" s="9" t="n"/>
       <c r="F113" s="10" t="n"/>
     </row>
-    <row r="114" ht="94" customHeight="1">
+    <row r="114" ht="199" customHeight="1">
       <c r="A114" s="11" t="inlineStr">
         <is>
           <t>備考</t>
@@ -6123,7 +6537,8 @@
           <t>休暇の days は申請作成（ONL-005）で土日・祝日を除き算出済みの値（半日は 0.5）をそのまま消化する。再計算しない。
 consume の契約（ONL-013 で定義）：失効日の早い付与行から順に used_days を加算（FIFO・行ロック）。不足なら BusinessException("E-004", "休暇残日数が不足しています。", 409)。UNLIMITED なら何もしない。days が null／0 以下は IllegalArgumentException（データ不整合 → E-012）。
 承認（1段目）時点では消化しない。差戻し・却下では消化も戻しも発生しない（消化は最終承認時のみ）。
-休暇の期間が付与行の失効日をまたぐ場合も、利用日は開始日で判定する（日ごとの按分は行わない）。</t>
+休暇の期間が付与行の失効日をまたぐ場合も、利用日は開始日で判定する（日ごとの按分は行わない）。
+休憩・離席修正（BREAK_CORRECTION）：AttendanceService#applyBreakCorrection(userId, workDate, kind, start, end) は @Transactional（承認のトランザクションに参加）。(1) attendance_records を FOR UPDATE で取得（無ければ null）→ checkBreakCorrection（ONL-005 で定義。出勤打刻なし／終了≦開始／出退勤の範囲外は E-003 400、他区間と重なれば E-005 409）→ (2) attendance_breaks で attendance_record_id の進行中（end_at IS NULL）区間を取得し、種別が同じならその行の start_at / end_at を申請値に更新（終了の押し忘れの補正）、そうでなければ新規 INSERT（kind, start_at, end_at）→ (3) clock_out がある日のみ calculate(clock_in, clock_out, spans) で work_minutes / overtime_minutes を再計算して保存。ログ「Break-correction applied」。corrected_break_kind/start/end は NULL にならない前提（申請時に必須チェック済み。NULL なら承認前の null 参照で E-012）。</t>
         </is>
       </c>
       <c r="C114" s="9" t="n"/>
@@ -6175,7 +6590,7 @@
       <c r="E118" s="9" t="n"/>
       <c r="F118" s="10" t="n"/>
     </row>
-    <row r="119" ht="19" customHeight="1">
+    <row r="119" ht="34" customHeight="1">
       <c r="A119" s="11" t="inlineStr">
         <is>
           <t>説明</t>
@@ -6183,7 +6598,7 @@
       </c>
       <c r="B119" s="7" t="inlineStr">
         <is>
-          <t>打刻修正申請の内容を attendance_records に反映する。対象日の打刻が無ければ新規作成する。</t>
+          <t>打刻修正申請の内容を attendance_records に反映する。対象日の打刻が無ければ新規作成し、その日の休憩・離席（attendance_breaks）を考慮して勤務・残業時間を再計算する。</t>
         </is>
       </c>
       <c r="C119" s="9" t="n"/>
@@ -6280,7 +6695,7 @@
       <c r="E124" s="9" t="n"/>
       <c r="F124" s="10" t="n"/>
     </row>
-    <row r="125" ht="244" customHeight="1">
+    <row r="125" ht="274" customHeight="1">
       <c r="A125" s="11" t="inlineStr">
         <is>
           <t>処理詳細</t>
@@ -6293,14 +6708,16 @@
 LocalDate workDate = req.getStartDate();                                // 対象日＝開始日（打刻修正は 1 日単位。end_date は startDate と同値＝ONL-005 D-2）
 AttendanceRecord rec = attendanceRecordRepository
         .findWithLockByUserIdAndWorkDate(req.getUserId(), workDate)     // SELECT … FOR UPDATE（ONL-002/003 と同じ）
-        .orElseGet(() -&gt; {                                              // 打刻漏れで未作成なら新規
-            AttendanceRecord n = new AttendanceRecord();
-            n.setUserId(req.getUserId()); n.setWorkDate(workDate); return n; });
+        .orElseGet(() -&gt; new AttendanceRecord(req.getUserId(), workDate)); // 打刻漏れで未作成なら新規（コンストラクタ引数で user_id / work_date を設定）
 rec.setClockIn(req.getCorrectedClockIn());
 rec.setClockOut(req.getCorrectedClockOut());
-WorkTime wt = attendanceCalculator.calculate(rec.getClockIn(), rec.getClockOut());   // 休憩控除（6h超45分/8h超60分）・残業=勤務−480
-rec.setWorkMinutes(wt.workMinutes());
-rec.setOvertimeMinutes(wt.overtimeMinutes());
+rec = attendanceRecordRepository.saveAndFlush(rec);                     // 新規の場合は id を確定させる（休憩区間の検索に使う）
+List&lt;AttendanceCalculator.Span&gt; spans = attendanceBreakRepository
+        .findByAttendanceRecordIdOrderByStartAtAsc(rec.getId()).stream()
+        .map(b -&gt; new AttendanceCalculator.Span(b.getKind(), b.getStartAt(), b.getEndAt())).toList();
+AttendanceCalculator.WorkTime wt = attendanceCalculator.calculate(rec.getClockIn(), rec.getClockOut(), spans);
+rec.setWorkMinutes(wt.workMinutes());                                   // 離席は全量控除、休憩は記録値（無ければ法定 45/60 分）
+rec.setOvertimeMinutes(wt.overtimeMinutes());                           // 勤務時間−480（負は0）
 attendanceRecordRepository.save(rec);</t>
         </is>
       </c>
@@ -6309,7 +6726,7 @@
       <c r="E125" s="9" t="n"/>
       <c r="F125" s="10" t="n"/>
     </row>
-    <row r="126" ht="19" customHeight="1">
+    <row r="126" ht="34" customHeight="1">
       <c r="A126" s="11" t="inlineStr">
         <is>
           <t>呼出先</t>
@@ -6317,7 +6734,7 @@
       </c>
       <c r="B126" s="7" t="inlineStr">
         <is>
-          <t>AttendanceRecordRepository#findWithLockByUserIdAndWorkDate / #save / AttendanceCalculator#calculate</t>
+          <t>AttendanceRecordRepository#findWithLockByUserIdAndWorkDate / #saveAndFlush / #save / AttendanceBreakRepository#findByAttendanceRecordIdOrderByStartAtAsc / AttendanceCalculator#calculate</t>
         </is>
       </c>
       <c r="C126" s="9" t="n"/>
@@ -6325,7 +6742,7 @@
       <c r="E126" s="9" t="n"/>
       <c r="F126" s="10" t="n"/>
     </row>
-    <row r="127" ht="64" customHeight="1">
+    <row r="127" ht="94" customHeight="1">
       <c r="A127" s="11" t="inlineStr">
         <is>
           <t>備考</t>
@@ -6336,7 +6753,8 @@
           <t>corrected_clock_in/out は TIMESTAMP（JST のローカル日時）。タイムゾーン変換は行わない。
 退勤が出勤より前の申請は ONL-005 の入力チェック（E-003）で弾かれている前提。calculate は負を 0 にする。
 打刻の行が無い日に、同時に出勤打刻（ONL-002）が INSERT されて UNIQUE 違反となった場合は E-012（全体ロールバック）。再操作で成功する。
-updated_at は DB トリガで自動更新される（Entity は設定しない）。</t>
+updated_at は DB トリガで自動更新される（Entity は設定しない）。
+修正後の出退勤の範囲外にある休憩・離席の区間は AttendanceCalculator が出退勤の範囲に切り詰めて計算する（区間自体は削除・変更しない）。未終了（end_at が NULL）の区間は計算から除外される。計算ルールの詳細は ONL-003。</t>
         </is>
       </c>
       <c r="C127" s="9" t="n"/>
@@ -6534,7 +6952,7 @@
       <c r="E139" s="9" t="n"/>
       <c r="F139" s="10" t="n"/>
     </row>
-    <row r="140" ht="274" customHeight="1">
+    <row r="140" ht="304" customHeight="1">
       <c r="A140" s="11" t="inlineStr">
         <is>
           <t>処理詳細</t>
@@ -6559,6 +6977,8 @@
           : req.getStartDate() + "〜" + req.getEndDate();          // LocalDate#toString＝yyyy-MM-dd
       return "休暇申請（" + period + "）";
   }
+  if (RequestType.BREAK_CORRECTION.equals(req.getRequestType()))
+      return "休憩・離席修正申請（対象日 " + req.getStartDate() + "）";
   return "打刻修正申請（対象日 " + req.getStartDate() + "）";</t>
         </is>
       </c>
@@ -6583,7 +7003,7 @@
       <c r="E141" s="9" t="n"/>
       <c r="F141" s="10" t="n"/>
     </row>
-    <row r="142" ht="124" customHeight="1">
+    <row r="142" ht="154" customHeight="1">
       <c r="A142" s="11" t="inlineStr">
         <is>
           <t>備考</t>
@@ -6594,7 +7014,8 @@
           <t>通知本文にコメントは含めない（500文字制限・情報の過剰露出を避ける。コメントは申請詳細の承認履歴で確認する）。文面の日付形式は ONL-005 の提出通知（yyyy-MM-dd）と揃える。
 notify は4引数（userId, type, message, requestId）で、type と申請ID（requestId）を notifications.type / request_id に保存する（疑似コードの定義元は ONL-005）。画面は requestId があれば SCR-106 の該当申請へ遷移する（ONL-019）。1段目承認と2段目承認はどちらも申請者宛の REQUEST_APPROVED だが、本文で区別する。
 resolveCurrentApproverIds は approver_id が設定済みならその1名、未設定（管理者段）なら有効な全管理者から申請者を除いた一覧を返す（ONL-005）。2段目は未処理のため後者。
-通知先が 0 件でもエラーにしない。</t>
+通知先が 0 件でもエラーにしない。
+通知本文の例：「休憩・離席修正申請（対象日 2026-10-01）が承認されました。」／「山田 太郎さんの休憩・離席修正申請（対象日 2026-10-01）の最終承認をお願いします。」</t>
         </is>
       </c>
       <c r="C142" s="9" t="n"/>
@@ -7895,51 +8316,115 @@
       <c r="E219" s="9" t="n"/>
       <c r="F219" s="10" t="n"/>
     </row>
-    <row r="221">
-      <c r="A221" s="8" t="inlineStr">
-        <is>
-          <t>6.16  ApprovalService のフィールド・定数（ONL-009〜012 共通）</t>
-        </is>
-      </c>
-      <c r="B221" s="9" t="n"/>
-      <c r="C221" s="9" t="n"/>
+    <row r="220" ht="49" customHeight="1">
+      <c r="A220" s="7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B220" s="7" t="inlineStr">
+        <is>
+          <t>休憩・離席修正（BREAK_CORRECTION）の最終承認</t>
+        </is>
+      </c>
+      <c r="C220" s="7" t="inlineStr">
+        <is>
+          <t>最終承認（2段目）で AttendanceService#applyBreakCorrection を呼び、attendance_breaks に反映する。1段目承認では何も反映しない。反映時にも申請時と同じ検証（checkBreakCorrection）を再実行し、不整合は E-003（400）／E-005（409）で全体ロールバック（ONL-005 D-19〜21）</t>
+        </is>
+      </c>
+      <c r="D220" s="9" t="n"/>
+      <c r="E220" s="9" t="n"/>
+      <c r="F220" s="10" t="n"/>
+    </row>
+    <row r="221" ht="49" customHeight="1">
+      <c r="A221" s="7" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B221" s="7" t="inlineStr">
+        <is>
+          <t>打刻修正と休憩・離席の整合</t>
+        </is>
+      </c>
+      <c r="C221" s="7" t="inlineStr">
+        <is>
+          <t>CLOCK_CORRECTION の最終承認でも、その日の attendance_breaks を読んで勤務・残業を再計算する（出退勤を変えても休憩・離席の控除が反映される）。区間そのものは変更しない。承認の順序で結果が変わらないよう、いずれの反映も最終的に calculate(in, out, 全区間) で再計算する</t>
+        </is>
+      </c>
       <c r="D221" s="9" t="n"/>
       <c r="E221" s="9" t="n"/>
       <c r="F221" s="10" t="n"/>
     </row>
-    <row r="222" ht="274" customHeight="1">
-      <c r="A222" s="11" t="inlineStr">
+    <row r="222" ht="19" customHeight="1">
+      <c r="A222" s="7" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B222" s="7" t="inlineStr">
+        <is>
+          <t>JWT の有効期間</t>
+        </is>
+      </c>
+      <c r="C222" s="7" t="inlineStr">
+        <is>
+          <t>JWT の有効期間は 2 時間。降格・無効化の反映は requireApprover の DB 再確認で行う（トークン失効では行わない）</t>
+        </is>
+      </c>
+      <c r="D222" s="9" t="n"/>
+      <c r="E222" s="9" t="n"/>
+      <c r="F222" s="10" t="n"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="8" t="inlineStr">
+        <is>
+          <t>6.16  ApprovalService のフィールド・定数（ONL-009〜012 共通）</t>
+        </is>
+      </c>
+      <c r="B224" s="9" t="n"/>
+      <c r="C224" s="9" t="n"/>
+      <c r="D224" s="9" t="n"/>
+      <c r="E224" s="9" t="n"/>
+      <c r="F224" s="10" t="n"/>
+    </row>
+    <row r="225" ht="334" customHeight="1">
+      <c r="A225" s="11" t="inlineStr">
         <is>
           <t>処理詳細</t>
         </is>
       </c>
-      <c r="B222" s="12" t="inlineStr">
+      <c r="B225" s="12" t="inlineStr">
         <is>
           <t>@Service
 public class ApprovalService {
     private static final Logger log = LoggerFactory.getLogger(ApprovalService.class);
-    private static final String ROLE_ADMIN = "ADMIN", ROLE_MANAGER = "MANAGER";
+    private static final String ROLE_ADMIN = "ADMIN", ROLE_MANAGER = "MANAGER", STATUS_ACTIVE = "ACTIVE";
     private final UserRepository userRepository;
     private final ApprovalStepRepository approvalStepRepository;
     private final RequestRepository requestRepository;
     private final AttendanceRecordRepository attendanceRecordRepository;
+    private final AttendanceBreakRepository attendanceBreakRepository;   // 打刻修正の再計算用（V4 以降）
     private final ApprovalRouteService approvalRouteService;
     private final LeaveBalanceService leaveBalanceService;
     private final AttendanceCalculator attendanceCalculator;
+    private final AttendanceService attendanceService;                   // 休憩・離席修正の反映 applyBreakCorrection
     private final NotificationService notificationService;
     private final Clock clock;                       // ClockConfig の Bean（Asia/Tokyo）
-    // コンストラクタインジェクション（@Autowired は付けない）
+    // コンストラクタインジェクション（@Autowired は付けない）。引数の順：approvalStepRepository, requestRepository, userRepository,
+    //   attendanceRecordRepository, attendanceBreakRepository, attendanceCalculator, attendanceService,
+    //   leaveBalanceService, approvalRouteService, notificationService, clock
     private record ApprovalContext(ApprovalStep step, Request request) {}
 }</t>
         </is>
       </c>
-      <c r="C222" s="9" t="n"/>
-      <c r="D222" s="9" t="n"/>
-      <c r="E222" s="9" t="n"/>
-      <c r="F222" s="10" t="n"/>
+      <c r="C225" s="9" t="n"/>
+      <c r="D225" s="9" t="n"/>
+      <c r="E225" s="9" t="n"/>
+      <c r="F225" s="10" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="206">
+  <mergeCells count="209">
     <mergeCell ref="A174:F174"/>
     <mergeCell ref="C52:F52"/>
     <mergeCell ref="B106:F106"/>
@@ -7966,6 +8451,7 @@
     <mergeCell ref="B60:F60"/>
     <mergeCell ref="A144:F144"/>
     <mergeCell ref="B170:F170"/>
+    <mergeCell ref="A224:F224"/>
     <mergeCell ref="C24:F24"/>
     <mergeCell ref="B53:F53"/>
     <mergeCell ref="C64:F64"/>
@@ -7985,6 +8471,7 @@
     <mergeCell ref="C164:F164"/>
     <mergeCell ref="B30:F30"/>
     <mergeCell ref="B158:F158"/>
+    <mergeCell ref="C221:F221"/>
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="B20:F20"/>
     <mergeCell ref="B15:F15"/>
@@ -7995,7 +8482,6 @@
     <mergeCell ref="B80:F80"/>
     <mergeCell ref="B160:F160"/>
     <mergeCell ref="C207:F207"/>
-    <mergeCell ref="A221:F221"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B125:F125"/>
     <mergeCell ref="C135:F135"/>
@@ -8038,6 +8524,7 @@
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="B85:F85"/>
     <mergeCell ref="B198:F198"/>
+    <mergeCell ref="C222:F222"/>
     <mergeCell ref="B188:F188"/>
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="B126:F126"/>
@@ -8067,6 +8554,7 @@
     <mergeCell ref="C108:F108"/>
     <mergeCell ref="B145:F145"/>
     <mergeCell ref="C166:F166"/>
+    <mergeCell ref="B225:F225"/>
     <mergeCell ref="B13:F13"/>
     <mergeCell ref="B191:F191"/>
     <mergeCell ref="B73:F73"/>
@@ -8085,7 +8573,6 @@
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="A45:F45"/>
     <mergeCell ref="A103:F103"/>
-    <mergeCell ref="B222:F222"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B63:F63"/>
     <mergeCell ref="B123:F123"/>
@@ -8112,6 +8599,7 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B86:F86"/>
     <mergeCell ref="B117:F117"/>
+    <mergeCell ref="C220:F220"/>
     <mergeCell ref="B151:F151"/>
     <mergeCell ref="C195:F195"/>
     <mergeCell ref="B61:F61"/>
@@ -8158,7 +8646,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:F94"/>
+  <dimension ref="A2:F105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -8649,7 +9137,7 @@
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>LEAVE / CLOCK_CORRECTION</t>
+          <t>LEAVE / CLOCK_CORRECTION / BREAK_CORRECTION</t>
         </is>
       </c>
     </row>
@@ -8869,288 +9357,288 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="19" customHeight="1">
+    <row r="26" ht="49" customHeight="1">
       <c r="A26" s="7" t="inlineStr">
         <is>
+          <t>corrected_break_kind / start / end</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>correctedBreakKind / Start / End</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>String / LocalDateTime</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>○ 休憩・離席修正の反映（kind, start, end）</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>BREAK_CORRECTION のみ（V5）。kind は BREAK / AWAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="19" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
           <t>reason</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>reason</t>
         </is>
       </c>
-      <c r="C26" s="7" t="inlineStr">
+      <c r="C27" s="7" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D26" s="7" t="inlineStr">
+      <c r="D27" s="7" t="inlineStr">
         <is>
           <t>可</t>
         </is>
       </c>
-      <c r="E26" s="7" t="inlineStr">
+      <c r="E27" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F26" s="7" t="inlineStr">
+      <c r="F27" s="7" t="inlineStr">
         <is>
           <t>VARCHAR(200)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="34" customHeight="1">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>不可</t>
-        </is>
-      </c>
-      <c r="E27" s="7" t="inlineStr">
-        <is>
-          <t>○ PENDING 確認／U APPROVED（2段目）</t>
-        </is>
-      </c>
-      <c r="F27" s="7" t="inlineStr">
-        <is>
-          <t>DRAFT / PENDING / RETURNED / REJECTED / APPROVED / WITHDRAWN</t>
         </is>
       </c>
     </row>
     <row r="28" ht="34" customHeight="1">
       <c r="A28" s="7" t="inlineStr">
         <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>○ PENDING 確認／U APPROVED（2段目）</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>DRAFT / PENDING / RETURNED / REJECTED / APPROVED / WITHDRAWN</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="34" customHeight="1">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
           <t>current_step</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>currentStep</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C29" s="7" t="inlineStr">
         <is>
           <t>Integer</t>
         </is>
       </c>
-      <c r="D28" s="7" t="inlineStr">
+      <c r="D29" s="7" t="inlineStr">
         <is>
           <t>不可</t>
         </is>
       </c>
-      <c r="E28" s="7" t="inlineStr">
+      <c r="E29" s="7" t="inlineStr">
         <is>
           <t>○ 照合／U 1→2（1段目）</t>
         </is>
       </c>
-      <c r="F28" s="7" t="inlineStr">
+      <c r="F29" s="7" t="inlineStr">
         <is>
           <t>現在の承認段（1/2）</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="19" customHeight="1">
-      <c r="A29" s="7" t="inlineStr">
+    <row r="30" ht="19" customHeight="1">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t>submitted_at</t>
         </is>
       </c>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t>submittedAt</t>
         </is>
       </c>
-      <c r="C29" s="7" t="inlineStr">
+      <c r="C30" s="7" t="inlineStr">
         <is>
           <t>LocalDateTime</t>
         </is>
       </c>
-      <c r="D29" s="7" t="inlineStr">
+      <c r="D30" s="7" t="inlineStr">
         <is>
           <t>可</t>
         </is>
       </c>
-      <c r="E29" s="7" t="inlineStr">
+      <c r="E30" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F29" s="7" t="inlineStr">
+      <c r="F30" s="7" t="inlineStr">
         <is>
           <t>提出日時（JST）</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="34" customHeight="1">
-      <c r="A30" s="7" t="inlineStr">
+    <row r="31" ht="34" customHeight="1">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="B30" s="7" t="inlineStr">
+      <c r="B31" s="7" t="inlineStr">
         <is>
           <t>createdAt</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
+      <c r="C31" s="7" t="inlineStr">
         <is>
           <t>LocalDateTime</t>
         </is>
       </c>
-      <c r="D30" s="7" t="inlineStr">
+      <c r="D31" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E30" s="7" t="inlineStr">
+      <c r="E31" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F30" s="7" t="inlineStr">
+      <c r="F31" s="7" t="inlineStr">
         <is>
           <t>DB の DEFAULT。insertable=false, updatable=false</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="64" customHeight="1">
-      <c r="A31" s="7" t="inlineStr">
+    <row r="32" ht="64" customHeight="1">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t>updated_at</t>
         </is>
       </c>
-      <c r="B31" s="7" t="inlineStr">
+      <c r="B32" s="7" t="inlineStr">
         <is>
           <t>updatedAt</t>
         </is>
       </c>
-      <c r="C31" s="7" t="inlineStr">
+      <c r="C32" s="7" t="inlineStr">
         <is>
           <t>LocalDateTime</t>
         </is>
       </c>
-      <c r="D31" s="7" t="inlineStr">
+      <c r="D32" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E31" s="7" t="inlineStr">
+      <c r="E32" s="7" t="inlineStr">
         <is>
           <t>— トリガで自動</t>
         </is>
       </c>
-      <c r="F31" s="7" t="inlineStr">
+      <c r="F32" s="7" t="inlineStr">
         <is>
           <t>DB トリガ trg_requests_updated_at（BEFORE UPDATE / set_updated_at）で更新時に自動更新。Entity は insertable=false, updatable=false（アプリは設定しない）</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="19" customHeight="1">
-      <c r="A32" s="11" t="inlineStr">
+    <row r="33" ht="19" customHeight="1">
+      <c r="A33" s="11" t="inlineStr">
         <is>
           <t>■ users</t>
         </is>
       </c>
-      <c r="B32" s="9" t="n"/>
-      <c r="C32" s="9" t="n"/>
-      <c r="D32" s="9" t="n"/>
-      <c r="E32" s="9" t="n"/>
-      <c r="F32" s="10" t="n"/>
-    </row>
-    <row r="33" ht="19" customHeight="1">
-      <c r="A33" s="6" t="inlineStr">
+      <c r="B33" s="9" t="n"/>
+      <c r="C33" s="9" t="n"/>
+      <c r="D33" s="9" t="n"/>
+      <c r="E33" s="9" t="n"/>
+      <c r="F33" s="10" t="n"/>
+    </row>
+    <row r="34" ht="19" customHeight="1">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>DB列</t>
         </is>
       </c>
-      <c r="B33" s="6" t="inlineStr">
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>Entityフィールド</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr">
+      <c r="C34" s="6" t="inlineStr">
         <is>
           <t>Java型</t>
         </is>
       </c>
-      <c r="D33" s="6" t="inlineStr">
+      <c r="D34" s="6" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
       </c>
-      <c r="E33" s="6" t="inlineStr">
+      <c r="E34" s="6" t="inlineStr">
         <is>
           <t>この処理での使用</t>
         </is>
       </c>
-      <c r="F33" s="6" t="inlineStr">
+      <c r="F34" s="6" t="inlineStr">
         <is>
           <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="19" customHeight="1">
-      <c r="A34" s="7" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="C34" s="7" t="inlineStr">
-        <is>
-          <t>Long</t>
-        </is>
-      </c>
-      <c r="D34" s="7" t="inlineStr">
-        <is>
-          <t>不可</t>
-        </is>
-      </c>
-      <c r="E34" s="7" t="inlineStr">
-        <is>
-          <t>○ 実行者の特定</t>
-        </is>
-      </c>
-      <c r="F34" s="7" t="inlineStr">
-        <is>
-          <t>IDENTITY 自動採番</t>
         </is>
       </c>
     </row>
     <row r="35" ht="19" customHeight="1">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>id</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
@@ -9160,24 +9648,24 @@
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>○ 実行者の特定</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>UNIQUE（uq_users_1）、VARCHAR(255)</t>
+          <t>IDENTITY 自動採番</t>
         </is>
       </c>
     </row>
     <row r="36" ht="19" customHeight="1">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>password_hash</t>
+          <t>email</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>passwordHash</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
@@ -9197,115 +9685,115 @@
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>BCrypt ハッシュ。VARCHAR(255)</t>
+          <t>UNIQUE（uq_users_1）、VARCHAR(255)</t>
         </is>
       </c>
     </row>
     <row r="37" ht="19" customHeight="1">
       <c r="A37" s="7" t="inlineStr">
         <is>
+          <t>password_hash</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>passwordHash</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>BCrypt ハッシュ。VARCHAR(255)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="19" customHeight="1">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
           <t>name</t>
         </is>
       </c>
-      <c r="B37" s="7" t="inlineStr">
+      <c r="B38" s="7" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C37" s="7" t="inlineStr">
+      <c r="C38" s="7" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D37" s="7" t="inlineStr">
+      <c r="D38" s="7" t="inlineStr">
         <is>
           <t>不可</t>
         </is>
       </c>
-      <c r="E37" s="7" t="inlineStr">
+      <c r="E38" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F37" s="7" t="inlineStr">
+      <c r="F38" s="7" t="inlineStr">
         <is>
           <t>VARCHAR(100)</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="34" customHeight="1">
-      <c r="A38" s="7" t="inlineStr">
+    <row r="39" ht="34" customHeight="1">
+      <c r="A39" s="7" t="inlineStr">
         <is>
           <t>role</t>
         </is>
       </c>
-      <c r="B38" s="7" t="inlineStr">
+      <c r="B39" s="7" t="inlineStr">
         <is>
           <t>role</t>
         </is>
       </c>
-      <c r="C38" s="7" t="inlineStr">
+      <c r="C39" s="7" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D38" s="7" t="inlineStr">
+      <c r="D39" s="7" t="inlineStr">
         <is>
           <t>不可</t>
         </is>
       </c>
-      <c r="E38" s="7" t="inlineStr">
+      <c r="E39" s="7" t="inlineStr">
         <is>
           <t>○ 実行者の権限確認・2段目の所有確認</t>
         </is>
       </c>
-      <c r="F38" s="7" t="inlineStr">
+      <c r="F39" s="7" t="inlineStr">
         <is>
           <t>EMPLOYEE / MANAGER / ADMIN</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="19" customHeight="1">
-      <c r="A39" s="7" t="inlineStr">
-        <is>
-          <t>department_id</t>
-        </is>
-      </c>
-      <c r="B39" s="7" t="inlineStr">
-        <is>
-          <t>departmentId</t>
-        </is>
-      </c>
-      <c r="C39" s="7" t="inlineStr">
-        <is>
-          <t>Long</t>
-        </is>
-      </c>
-      <c r="D39" s="7" t="inlineStr">
-        <is>
-          <t>可</t>
-        </is>
-      </c>
-      <c r="E39" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F39" s="7" t="inlineStr">
-        <is>
-          <t>FK departments</t>
         </is>
       </c>
     </row>
     <row r="40" ht="19" customHeight="1">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>manager_id</t>
+          <t>department_id</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>managerId</t>
+          <t>departmentId</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
@@ -9325,29 +9813,29 @@
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>FK users</t>
+          <t>FK departments</t>
         </is>
       </c>
     </row>
     <row r="41" ht="19" customHeight="1">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>hire_date</t>
+          <t>manager_id</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>hireDate</t>
+          <t>managerId</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>LocalDate</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>不可</t>
+          <t>可</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
@@ -9355,322 +9843,322 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F41" s="7" t="inlineStr"/>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>FK users</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="19" customHeight="1">
       <c r="A42" s="7" t="inlineStr">
         <is>
+          <t>hire_date</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>hireDate</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>LocalDate</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr"/>
+    </row>
+    <row r="43" ht="19" customHeight="1">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
           <t>status</t>
         </is>
       </c>
-      <c r="B42" s="7" t="inlineStr">
+      <c r="B43" s="7" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="C42" s="7" t="inlineStr">
+      <c r="C43" s="7" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D42" s="7" t="inlineStr">
+      <c r="D43" s="7" t="inlineStr">
         <is>
           <t>不可</t>
         </is>
       </c>
-      <c r="E42" s="7" t="inlineStr">
+      <c r="E43" s="7" t="inlineStr">
         <is>
           <t>○ 実行者の有効確認</t>
         </is>
       </c>
-      <c r="F42" s="7" t="inlineStr">
+      <c r="F43" s="7" t="inlineStr">
         <is>
           <t>ACTIVE / INACTIVE（既定 ACTIVE）</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="34" customHeight="1">
-      <c r="A43" s="7" t="inlineStr">
+    <row r="44" ht="34" customHeight="1">
+      <c r="A44" s="7" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="B43" s="7" t="inlineStr">
+      <c r="B44" s="7" t="inlineStr">
         <is>
           <t>createdAt</t>
         </is>
       </c>
-      <c r="C43" s="7" t="inlineStr">
+      <c r="C44" s="7" t="inlineStr">
         <is>
           <t>LocalDateTime</t>
         </is>
       </c>
-      <c r="D43" s="7" t="inlineStr">
+      <c r="D44" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E43" s="7" t="inlineStr">
+      <c r="E44" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F43" s="7" t="inlineStr">
+      <c r="F44" s="7" t="inlineStr">
         <is>
           <t>DB の DEFAULT。insertable=false, updatable=false</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="64" customHeight="1">
-      <c r="A44" s="7" t="inlineStr">
+    <row r="45" ht="64" customHeight="1">
+      <c r="A45" s="7" t="inlineStr">
         <is>
           <t>updated_at</t>
         </is>
       </c>
-      <c r="B44" s="7" t="inlineStr">
+      <c r="B45" s="7" t="inlineStr">
         <is>
           <t>updatedAt</t>
         </is>
       </c>
-      <c r="C44" s="7" t="inlineStr">
+      <c r="C45" s="7" t="inlineStr">
         <is>
           <t>LocalDateTime</t>
         </is>
       </c>
-      <c r="D44" s="7" t="inlineStr">
+      <c r="D45" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E44" s="7" t="inlineStr">
+      <c r="E45" s="7" t="inlineStr">
         <is>
           <t>— トリガで自動</t>
         </is>
       </c>
-      <c r="F44" s="7" t="inlineStr">
+      <c r="F45" s="7" t="inlineStr">
         <is>
           <t>DB トリガ trg_users_updated_at（BEFORE UPDATE / set_updated_at）で更新時に自動更新。Entity は insertable=false, updatable=false（アプリは設定しない）</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="19" customHeight="1">
-      <c r="A45" s="11" t="inlineStr">
+    <row r="46" ht="19" customHeight="1">
+      <c r="A46" s="11" t="inlineStr">
         <is>
           <t>■ leave_balances</t>
         </is>
       </c>
-      <c r="B45" s="9" t="n"/>
-      <c r="C45" s="9" t="n"/>
-      <c r="D45" s="9" t="n"/>
-      <c r="E45" s="9" t="n"/>
-      <c r="F45" s="10" t="n"/>
-    </row>
-    <row r="46" ht="19" customHeight="1">
-      <c r="A46" s="6" t="inlineStr">
+      <c r="B46" s="9" t="n"/>
+      <c r="C46" s="9" t="n"/>
+      <c r="D46" s="9" t="n"/>
+      <c r="E46" s="9" t="n"/>
+      <c r="F46" s="10" t="n"/>
+    </row>
+    <row r="47" ht="19" customHeight="1">
+      <c r="A47" s="6" t="inlineStr">
         <is>
           <t>DB列</t>
         </is>
       </c>
-      <c r="B46" s="6" t="inlineStr">
+      <c r="B47" s="6" t="inlineStr">
         <is>
           <t>Entityフィールド</t>
         </is>
       </c>
-      <c r="C46" s="6" t="inlineStr">
+      <c r="C47" s="6" t="inlineStr">
         <is>
           <t>Java型</t>
         </is>
       </c>
-      <c r="D46" s="6" t="inlineStr">
+      <c r="D47" s="6" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
       </c>
-      <c r="E46" s="6" t="inlineStr">
+      <c r="E47" s="6" t="inlineStr">
         <is>
           <t>この処理での使用</t>
         </is>
       </c>
-      <c r="F46" s="6" t="inlineStr">
+      <c r="F47" s="6" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="19" customHeight="1">
-      <c r="A47" s="7" t="inlineStr">
+    <row r="48" ht="19" customHeight="1">
+      <c r="A48" s="7" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B47" s="7" t="inlineStr">
+      <c r="B48" s="7" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C47" s="7" t="inlineStr">
+      <c r="C48" s="7" t="inlineStr">
         <is>
           <t>Long</t>
         </is>
       </c>
-      <c r="D47" s="7" t="inlineStr">
+      <c r="D48" s="7" t="inlineStr">
         <is>
           <t>不可</t>
         </is>
       </c>
-      <c r="E47" s="7" t="inlineStr">
+      <c r="E48" s="7" t="inlineStr">
         <is>
           <t>○ 更新対象</t>
         </is>
       </c>
-      <c r="F47" s="7" t="inlineStr">
+      <c r="F48" s="7" t="inlineStr">
         <is>
           <t>IDENTITY 自動採番</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="34" customHeight="1">
-      <c r="A48" s="7" t="inlineStr">
+    <row r="49" ht="34" customHeight="1">
+      <c r="A49" s="7" t="inlineStr">
         <is>
           <t>user_id</t>
         </is>
       </c>
-      <c r="B48" s="7" t="inlineStr">
+      <c r="B49" s="7" t="inlineStr">
         <is>
           <t>userId</t>
         </is>
       </c>
-      <c r="C48" s="7" t="inlineStr">
+      <c r="C49" s="7" t="inlineStr">
         <is>
           <t>Long</t>
         </is>
       </c>
-      <c r="D48" s="7" t="inlineStr">
+      <c r="D49" s="7" t="inlineStr">
         <is>
           <t>不可</t>
         </is>
       </c>
-      <c r="E48" s="7" t="inlineStr">
+      <c r="E49" s="7" t="inlineStr">
         <is>
           <t>○ 消化対象の検索（LeaveBalanceService）</t>
         </is>
       </c>
-      <c r="F48" s="7" t="inlineStr">
+      <c r="F49" s="7" t="inlineStr">
         <is>
           <t>FK users</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="19" customHeight="1">
-      <c r="A49" s="7" t="inlineStr">
-        <is>
-          <t>leave_type_id</t>
-        </is>
-      </c>
-      <c r="B49" s="7" t="inlineStr">
-        <is>
-          <t>leaveTypeId</t>
-        </is>
-      </c>
-      <c r="C49" s="7" t="inlineStr">
-        <is>
-          <t>Long</t>
-        </is>
-      </c>
-      <c r="D49" s="7" t="inlineStr">
-        <is>
-          <t>不可</t>
-        </is>
-      </c>
-      <c r="E49" s="7" t="inlineStr">
-        <is>
-          <t>○ 同上</t>
-        </is>
-      </c>
-      <c r="F49" s="7" t="inlineStr">
-        <is>
-          <t>FK leave_types</t>
         </is>
       </c>
     </row>
     <row r="50" ht="19" customHeight="1">
       <c r="A50" s="7" t="inlineStr">
         <is>
+          <t>leave_type_id</t>
+        </is>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>leaveTypeId</t>
+        </is>
+      </c>
+      <c r="C50" s="7" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>○ 同上</t>
+        </is>
+      </c>
+      <c r="F50" s="7" t="inlineStr">
+        <is>
+          <t>FK leave_types</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="19" customHeight="1">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
           <t>granted_days</t>
         </is>
       </c>
-      <c r="B50" s="7" t="inlineStr">
+      <c r="B51" s="7" t="inlineStr">
         <is>
           <t>grantedDays</t>
         </is>
       </c>
-      <c r="C50" s="7" t="inlineStr">
+      <c r="C51" s="7" t="inlineStr">
         <is>
           <t>BigDecimal</t>
         </is>
       </c>
-      <c r="D50" s="7" t="inlineStr">
+      <c r="D51" s="7" t="inlineStr">
         <is>
           <t>不可</t>
         </is>
       </c>
-      <c r="E50" s="7" t="inlineStr">
+      <c r="E51" s="7" t="inlineStr">
         <is>
           <t>○ 残の算出</t>
         </is>
       </c>
-      <c r="F50" s="7" t="inlineStr">
+      <c r="F51" s="7" t="inlineStr">
         <is>
           <t>DECIMAL(4,1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="34" customHeight="1">
-      <c r="A51" s="7" t="inlineStr">
-        <is>
-          <t>used_days</t>
-        </is>
-      </c>
-      <c r="B51" s="7" t="inlineStr">
-        <is>
-          <t>usedDays</t>
-        </is>
-      </c>
-      <c r="C51" s="7" t="inlineStr">
-        <is>
-          <t>BigDecimal</t>
-        </is>
-      </c>
-      <c r="D51" s="7" t="inlineStr">
-        <is>
-          <t>不可</t>
-        </is>
-      </c>
-      <c r="E51" s="7" t="inlineStr">
-        <is>
-          <t>U 消化日数を加算（FIFO）</t>
-        </is>
-      </c>
-      <c r="F51" s="7" t="inlineStr">
-        <is>
-          <t>DECIMAL(4,1)、既定 0。消化の詳細は ONL-013 の LeaveBalanceService#consume</t>
         </is>
       </c>
     </row>
     <row r="52" ht="34" customHeight="1">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>granted_on</t>
+          <t>used_days</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>grantedOn</t>
+          <t>usedDays</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>LocalDate</t>
+          <t>BigDecimal</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
@@ -9680,20 +10168,24 @@
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>○ 利用日が付与日以降かの判定</t>
-        </is>
-      </c>
-      <c r="F52" s="7" t="inlineStr"/>
+          <t>U 消化日数を加算（FIFO）</t>
+        </is>
+      </c>
+      <c r="F52" s="7" t="inlineStr">
+        <is>
+          <t>DECIMAL(4,1)、既定 0。消化の詳細は ONL-013 の LeaveBalanceService#consume</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="34" customHeight="1">
       <c r="A53" s="7" t="inlineStr">
         <is>
-          <t>expires_on</t>
+          <t>granted_on</t>
         </is>
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>expiresOn</t>
+          <t>grantedOn</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
@@ -9708,496 +10200,492 @@
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t>○ 有効期限判定・消化順</t>
-        </is>
-      </c>
-      <c r="F53" s="7" t="inlineStr">
-        <is>
-          <t>付与日＋2年</t>
-        </is>
-      </c>
+          <t>○ 利用日が付与日以降かの判定</t>
+        </is>
+      </c>
+      <c r="F53" s="7" t="inlineStr"/>
     </row>
     <row r="54" ht="34" customHeight="1">
       <c r="A54" s="7" t="inlineStr">
         <is>
+          <t>expires_on</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>expiresOn</t>
+        </is>
+      </c>
+      <c r="C54" s="7" t="inlineStr">
+        <is>
+          <t>LocalDate</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t>○ 有効期限判定・消化順</t>
+        </is>
+      </c>
+      <c r="F54" s="7" t="inlineStr">
+        <is>
+          <t>付与日＋2年</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="34" customHeight="1">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="B54" s="7" t="inlineStr">
+      <c r="B55" s="7" t="inlineStr">
         <is>
           <t>createdAt</t>
         </is>
       </c>
-      <c r="C54" s="7" t="inlineStr">
+      <c r="C55" s="7" t="inlineStr">
         <is>
           <t>LocalDateTime</t>
         </is>
       </c>
-      <c r="D54" s="7" t="inlineStr">
+      <c r="D55" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E54" s="7" t="inlineStr">
+      <c r="E55" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F54" s="7" t="inlineStr">
+      <c r="F55" s="7" t="inlineStr">
         <is>
           <t>DB の DEFAULT。insertable=false, updatable=false</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="64" customHeight="1">
-      <c r="A55" s="7" t="inlineStr">
+    <row r="56" ht="64" customHeight="1">
+      <c r="A56" s="7" t="inlineStr">
         <is>
           <t>updated_at</t>
         </is>
       </c>
-      <c r="B55" s="7" t="inlineStr">
+      <c r="B56" s="7" t="inlineStr">
         <is>
           <t>updatedAt</t>
         </is>
       </c>
-      <c r="C55" s="7" t="inlineStr">
+      <c r="C56" s="7" t="inlineStr">
         <is>
           <t>LocalDateTime</t>
         </is>
       </c>
-      <c r="D55" s="7" t="inlineStr">
+      <c r="D56" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E55" s="7" t="inlineStr">
+      <c r="E56" s="7" t="inlineStr">
         <is>
           <t>— トリガで自動</t>
         </is>
       </c>
-      <c r="F55" s="7" t="inlineStr">
+      <c r="F56" s="7" t="inlineStr">
         <is>
           <t>DB トリガ trg_leave_balances_updated_at（BEFORE UPDATE / set_updated_at）で更新時に自動更新。Entity は insertable=false, updatable=false（アプリは設定しない）</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="19" customHeight="1">
-      <c r="A56" s="11" t="inlineStr">
+    <row r="57" ht="19" customHeight="1">
+      <c r="A57" s="11" t="inlineStr">
         <is>
           <t>■ attendance_records</t>
         </is>
       </c>
-      <c r="B56" s="9" t="n"/>
-      <c r="C56" s="9" t="n"/>
-      <c r="D56" s="9" t="n"/>
-      <c r="E56" s="9" t="n"/>
-      <c r="F56" s="10" t="n"/>
-    </row>
-    <row r="57" ht="19" customHeight="1">
-      <c r="A57" s="6" t="inlineStr">
+      <c r="B57" s="9" t="n"/>
+      <c r="C57" s="9" t="n"/>
+      <c r="D57" s="9" t="n"/>
+      <c r="E57" s="9" t="n"/>
+      <c r="F57" s="10" t="n"/>
+    </row>
+    <row r="58" ht="19" customHeight="1">
+      <c r="A58" s="6" t="inlineStr">
         <is>
           <t>DB列</t>
         </is>
       </c>
-      <c r="B57" s="6" t="inlineStr">
+      <c r="B58" s="6" t="inlineStr">
         <is>
           <t>Entityフィールド</t>
         </is>
       </c>
-      <c r="C57" s="6" t="inlineStr">
+      <c r="C58" s="6" t="inlineStr">
         <is>
           <t>Java型</t>
         </is>
       </c>
-      <c r="D57" s="6" t="inlineStr">
+      <c r="D58" s="6" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
       </c>
-      <c r="E57" s="6" t="inlineStr">
+      <c r="E58" s="6" t="inlineStr">
         <is>
           <t>この処理での使用</t>
         </is>
       </c>
-      <c r="F57" s="6" t="inlineStr">
+      <c r="F58" s="6" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="19" customHeight="1">
-      <c r="A58" s="7" t="inlineStr">
+    <row r="59" ht="19" customHeight="1">
+      <c r="A59" s="7" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B58" s="7" t="inlineStr">
+      <c r="B59" s="7" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C58" s="7" t="inlineStr">
+      <c r="C59" s="7" t="inlineStr">
         <is>
           <t>Long</t>
         </is>
       </c>
-      <c r="D58" s="7" t="inlineStr">
+      <c r="D59" s="7" t="inlineStr">
         <is>
           <t>不可</t>
         </is>
       </c>
-      <c r="E58" s="7" t="inlineStr">
+      <c r="E59" s="7" t="inlineStr">
         <is>
           <t>○ 更新対象</t>
         </is>
       </c>
-      <c r="F58" s="7" t="inlineStr">
+      <c r="F59" s="7" t="inlineStr">
         <is>
           <t>IDENTITY 自動採番</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="34" customHeight="1">
-      <c r="A59" s="7" t="inlineStr">
-        <is>
-          <t>user_id</t>
-        </is>
-      </c>
-      <c r="B59" s="7" t="inlineStr">
-        <is>
-          <t>userId</t>
-        </is>
-      </c>
-      <c r="C59" s="7" t="inlineStr">
-        <is>
-          <t>Long</t>
-        </is>
-      </c>
-      <c r="D59" s="7" t="inlineStr">
-        <is>
-          <t>不可</t>
-        </is>
-      </c>
-      <c r="E59" s="7" t="inlineStr">
-        <is>
-          <t>○ 検索条件／C 新規時に設定</t>
-        </is>
-      </c>
-      <c r="F59" s="7" t="inlineStr">
-        <is>
-          <t>FK users。UNIQUE（user_id, work_date）</t>
         </is>
       </c>
     </row>
     <row r="60" ht="34" customHeight="1">
       <c r="A60" s="7" t="inlineStr">
         <is>
+          <t>user_id</t>
+        </is>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>userId</t>
+        </is>
+      </c>
+      <c r="C60" s="7" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="D60" s="7" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t>○ 検索条件／C 新規時に設定</t>
+        </is>
+      </c>
+      <c r="F60" s="7" t="inlineStr">
+        <is>
+          <t>FK users。UNIQUE（user_id, work_date）</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="34" customHeight="1">
+      <c r="A61" s="7" t="inlineStr">
+        <is>
           <t>work_date</t>
         </is>
       </c>
-      <c r="B60" s="7" t="inlineStr">
+      <c r="B61" s="7" t="inlineStr">
         <is>
           <t>workDate</t>
         </is>
       </c>
-      <c r="C60" s="7" t="inlineStr">
+      <c r="C61" s="7" t="inlineStr">
         <is>
           <t>LocalDate</t>
         </is>
       </c>
-      <c r="D60" s="7" t="inlineStr">
+      <c r="D61" s="7" t="inlineStr">
         <is>
           <t>不可</t>
         </is>
       </c>
-      <c r="E60" s="7" t="inlineStr">
+      <c r="E61" s="7" t="inlineStr">
         <is>
           <t>○ 検索条件（= requests.start_date）／C</t>
         </is>
       </c>
-      <c r="F60" s="7" t="inlineStr">
+      <c r="F61" s="7" t="inlineStr">
         <is>
           <t>同上</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="19" customHeight="1">
-      <c r="A61" s="7" t="inlineStr">
-        <is>
-          <t>clock_in</t>
-        </is>
-      </c>
-      <c r="B61" s="7" t="inlineStr">
-        <is>
-          <t>clockIn</t>
-        </is>
-      </c>
-      <c r="C61" s="7" t="inlineStr">
-        <is>
-          <t>LocalDateTime</t>
-        </is>
-      </c>
-      <c r="D61" s="7" t="inlineStr">
-        <is>
-          <t>可</t>
-        </is>
-      </c>
-      <c r="E61" s="7" t="inlineStr">
-        <is>
-          <t>U 修正後の出勤</t>
-        </is>
-      </c>
-      <c r="F61" s="7" t="inlineStr">
-        <is>
-          <t>JST</t>
         </is>
       </c>
     </row>
     <row r="62" ht="19" customHeight="1">
       <c r="A62" s="7" t="inlineStr">
         <is>
+          <t>clock_in</t>
+        </is>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>clockIn</t>
+        </is>
+      </c>
+      <c r="C62" s="7" t="inlineStr">
+        <is>
+          <t>LocalDateTime</t>
+        </is>
+      </c>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>U 修正後の出勤</t>
+        </is>
+      </c>
+      <c r="F62" s="7" t="inlineStr">
+        <is>
+          <t>JST</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="19" customHeight="1">
+      <c r="A63" s="7" t="inlineStr">
+        <is>
           <t>clock_out</t>
         </is>
       </c>
-      <c r="B62" s="7" t="inlineStr">
+      <c r="B63" s="7" t="inlineStr">
         <is>
           <t>clockOut</t>
         </is>
       </c>
-      <c r="C62" s="7" t="inlineStr">
+      <c r="C63" s="7" t="inlineStr">
         <is>
           <t>LocalDateTime</t>
         </is>
       </c>
-      <c r="D62" s="7" t="inlineStr">
+      <c r="D63" s="7" t="inlineStr">
         <is>
           <t>可</t>
         </is>
       </c>
-      <c r="E62" s="7" t="inlineStr">
+      <c r="E63" s="7" t="inlineStr">
         <is>
           <t>U 修正後の退勤</t>
         </is>
       </c>
-      <c r="F62" s="7" t="inlineStr">
+      <c r="F63" s="7" t="inlineStr">
         <is>
           <t>JST</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="34" customHeight="1">
-      <c r="A63" s="7" t="inlineStr">
+    <row r="64" ht="49" customHeight="1">
+      <c r="A64" s="7" t="inlineStr">
         <is>
           <t>work_minutes</t>
         </is>
       </c>
-      <c r="B63" s="7" t="inlineStr">
+      <c r="B64" s="7" t="inlineStr">
         <is>
           <t>workMinutes</t>
         </is>
       </c>
-      <c r="C63" s="7" t="inlineStr">
+      <c r="C64" s="7" t="inlineStr">
         <is>
           <t>Integer</t>
         </is>
       </c>
-      <c r="D63" s="7" t="inlineStr">
+      <c r="D64" s="7" t="inlineStr">
         <is>
           <t>可</t>
         </is>
       </c>
-      <c r="E63" s="7" t="inlineStr">
-        <is>
-          <t>U AttendanceCalculator の結果</t>
-        </is>
-      </c>
-      <c r="F63" s="7" t="inlineStr">
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>U AttendanceCalculator の結果（休憩・離席の区間を考慮）</t>
+        </is>
+      </c>
+      <c r="F64" s="7" t="inlineStr">
         <is>
           <t>勤務時間（分）。休憩控除後</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="19" customHeight="1">
-      <c r="A64" s="7" t="inlineStr">
+    <row r="65" ht="19" customHeight="1">
+      <c r="A65" s="7" t="inlineStr">
         <is>
           <t>overtime_minutes</t>
         </is>
       </c>
-      <c r="B64" s="7" t="inlineStr">
+      <c r="B65" s="7" t="inlineStr">
         <is>
           <t>overtimeMinutes</t>
         </is>
       </c>
-      <c r="C64" s="7" t="inlineStr">
+      <c r="C65" s="7" t="inlineStr">
         <is>
           <t>Integer</t>
         </is>
       </c>
-      <c r="D64" s="7" t="inlineStr">
+      <c r="D65" s="7" t="inlineStr">
         <is>
           <t>可</t>
         </is>
       </c>
-      <c r="E64" s="7" t="inlineStr">
+      <c r="E65" s="7" t="inlineStr">
         <is>
           <t>U 同上</t>
         </is>
       </c>
-      <c r="F64" s="7" t="inlineStr">
+      <c r="F65" s="7" t="inlineStr">
         <is>
           <t>残業時間（分）。勤務時間−480（負は0）</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="34" customHeight="1">
-      <c r="A65" s="7" t="inlineStr">
+    <row r="66" ht="34" customHeight="1">
+      <c r="A66" s="7" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="B65" s="7" t="inlineStr">
+      <c r="B66" s="7" t="inlineStr">
         <is>
           <t>createdAt</t>
         </is>
       </c>
-      <c r="C65" s="7" t="inlineStr">
+      <c r="C66" s="7" t="inlineStr">
         <is>
           <t>LocalDateTime</t>
         </is>
       </c>
-      <c r="D65" s="7" t="inlineStr">
+      <c r="D66" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E65" s="7" t="inlineStr">
+      <c r="E66" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F65" s="7" t="inlineStr">
+      <c r="F66" s="7" t="inlineStr">
         <is>
           <t>DB の DEFAULT。insertable=false, updatable=false</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="64" customHeight="1">
-      <c r="A66" s="7" t="inlineStr">
+    <row r="67" ht="64" customHeight="1">
+      <c r="A67" s="7" t="inlineStr">
         <is>
           <t>updated_at</t>
         </is>
       </c>
-      <c r="B66" s="7" t="inlineStr">
+      <c r="B67" s="7" t="inlineStr">
         <is>
           <t>updatedAt</t>
         </is>
       </c>
-      <c r="C66" s="7" t="inlineStr">
+      <c r="C67" s="7" t="inlineStr">
         <is>
           <t>LocalDateTime</t>
         </is>
       </c>
-      <c r="D66" s="7" t="inlineStr">
+      <c r="D67" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E66" s="7" t="inlineStr">
+      <c r="E67" s="7" t="inlineStr">
         <is>
           <t>— トリガで自動</t>
         </is>
       </c>
-      <c r="F66" s="7" t="inlineStr">
+      <c r="F67" s="7" t="inlineStr">
         <is>
           <t>DB トリガ trg_attendance_records_updated_at（BEFORE UPDATE / set_updated_at）で更新時に自動更新。Entity は insertable=false, updatable=false（アプリは設定しない）</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="19" customHeight="1">
-      <c r="A67" s="11" t="inlineStr">
-        <is>
-          <t>■ notifications</t>
-        </is>
-      </c>
-      <c r="B67" s="9" t="n"/>
-      <c r="C67" s="9" t="n"/>
-      <c r="D67" s="9" t="n"/>
-      <c r="E67" s="9" t="n"/>
-      <c r="F67" s="10" t="n"/>
-    </row>
     <row r="68" ht="19" customHeight="1">
-      <c r="A68" s="6" t="inlineStr">
+      <c r="A68" s="11" t="inlineStr">
+        <is>
+          <t>■ attendance_breaks</t>
+        </is>
+      </c>
+      <c r="B68" s="9" t="n"/>
+      <c r="C68" s="9" t="n"/>
+      <c r="D68" s="9" t="n"/>
+      <c r="E68" s="9" t="n"/>
+      <c r="F68" s="10" t="n"/>
+    </row>
+    <row r="69" ht="19" customHeight="1">
+      <c r="A69" s="6" t="inlineStr">
         <is>
           <t>DB列</t>
         </is>
       </c>
-      <c r="B68" s="6" t="inlineStr">
+      <c r="B69" s="6" t="inlineStr">
         <is>
           <t>Entityフィールド</t>
         </is>
       </c>
-      <c r="C68" s="6" t="inlineStr">
+      <c r="C69" s="6" t="inlineStr">
         <is>
           <t>Java型</t>
         </is>
       </c>
-      <c r="D68" s="6" t="inlineStr">
+      <c r="D69" s="6" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
       </c>
-      <c r="E68" s="6" t="inlineStr">
+      <c r="E69" s="6" t="inlineStr">
         <is>
           <t>この処理での使用</t>
         </is>
       </c>
-      <c r="F68" s="6" t="inlineStr">
+      <c r="F69" s="6" t="inlineStr">
         <is>
           <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="34" customHeight="1">
-      <c r="A69" s="7" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="B69" s="7" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="C69" s="7" t="inlineStr">
-        <is>
-          <t>Long</t>
-        </is>
-      </c>
-      <c r="D69" s="7" t="inlineStr">
-        <is>
-          <t>不可</t>
-        </is>
-      </c>
-      <c r="E69" s="7" t="inlineStr">
-        <is>
-          <t>—（INSERT 後に採番）</t>
-        </is>
-      </c>
-      <c r="F69" s="7" t="inlineStr">
-        <is>
-          <t>IDENTITY 自動採番</t>
         </is>
       </c>
     </row>
     <row r="70" ht="34" customHeight="1">
       <c r="A70" s="7" t="inlineStr">
         <is>
-          <t>user_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="B70" s="7" t="inlineStr">
         <is>
-          <t>userId</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
@@ -10212,140 +10700,140 @@
       </c>
       <c r="E70" s="7" t="inlineStr">
         <is>
-          <t>C 通知先（申請者／管理者）</t>
+          <t>○ 更新対象（進行中の区間）</t>
         </is>
       </c>
       <c r="F70" s="7" t="inlineStr">
         <is>
-          <t>FK users（通知先）。登録は NotificationService#notify（ONL-005 定義）</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="49" customHeight="1">
+          <t>IDENTITY 自動採番</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="34" customHeight="1">
       <c r="A71" s="7" t="inlineStr">
         <is>
-          <t>type</t>
+          <t>attendance_record_id</t>
         </is>
       </c>
       <c r="B71" s="7" t="inlineStr">
         <is>
-          <t>type</t>
+          <t>attendanceRecordId</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>可</t>
+          <t>不可</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
-          <t>C 登録（REQUEST_APPROVED / REQUEST_SUBMITTED）</t>
+          <t>○ 検索条件／C 新規区間に設定</t>
         </is>
       </c>
       <c r="F71" s="7" t="inlineStr">
         <is>
-          <t>VARCHAR(30)。NotificationType の値（REQUEST_SUBMITTED ほか7種。KF-BD-005）</t>
+          <t>FK attendance_records（ON DELETE CASCADE）</t>
         </is>
       </c>
     </row>
     <row r="72" ht="34" customHeight="1">
       <c r="A72" s="7" t="inlineStr">
         <is>
-          <t>request_id</t>
+          <t>kind</t>
         </is>
       </c>
       <c r="B72" s="7" t="inlineStr">
         <is>
-          <t>requestId</t>
+          <t>kind</t>
         </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t>○ 同種別の進行中区間の判定／C 設定</t>
+        </is>
+      </c>
+      <c r="F72" s="7" t="inlineStr">
+        <is>
+          <t>BREAK / AWAY（CHECK）</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="34" customHeight="1">
+      <c r="A73" s="7" t="inlineStr">
+        <is>
+          <t>start_at</t>
+        </is>
+      </c>
+      <c r="B73" s="7" t="inlineStr">
+        <is>
+          <t>startAt</t>
+        </is>
+      </c>
+      <c r="C73" s="7" t="inlineStr">
+        <is>
+          <t>LocalDateTime</t>
+        </is>
+      </c>
+      <c r="D73" s="7" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="E73" s="7" t="inlineStr">
+        <is>
+          <t>○ 重なり判定・再計算／U 修正後の開始／C</t>
+        </is>
+      </c>
+      <c r="F73" s="7" t="inlineStr">
+        <is>
+          <t>JST</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="49" customHeight="1">
+      <c r="A74" s="7" t="inlineStr">
+        <is>
+          <t>end_at</t>
+        </is>
+      </c>
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t>endAt</t>
+        </is>
+      </c>
+      <c r="C74" s="7" t="inlineStr">
+        <is>
+          <t>LocalDateTime</t>
+        </is>
+      </c>
+      <c r="D74" s="7" t="inlineStr">
+        <is>
           <t>可</t>
         </is>
       </c>
-      <c r="E72" s="7" t="inlineStr">
-        <is>
-          <t>C 登録（申請ID）</t>
-        </is>
-      </c>
-      <c r="F72" s="7" t="inlineStr">
-        <is>
-          <t>FK requests(id)。申請に紐づかない通知（LEAVE_*）は NULL</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="19" customHeight="1">
-      <c r="A73" s="7" t="inlineStr">
-        <is>
-          <t>message</t>
-        </is>
-      </c>
-      <c r="B73" s="7" t="inlineStr">
-        <is>
-          <t>message</t>
-        </is>
-      </c>
-      <c r="C73" s="7" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="D73" s="7" t="inlineStr">
-        <is>
-          <t>不可</t>
-        </is>
-      </c>
-      <c r="E73" s="7" t="inlineStr">
-        <is>
-          <t>C 通知本文</t>
-        </is>
-      </c>
-      <c r="F73" s="7" t="inlineStr">
-        <is>
-          <t>VARCHAR(500)</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="34" customHeight="1">
-      <c r="A74" s="7" t="inlineStr">
-        <is>
-          <t>is_read</t>
-        </is>
-      </c>
-      <c r="B74" s="7" t="inlineStr">
-        <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="C74" s="7" t="inlineStr">
-        <is>
-          <t>boolean</t>
-        </is>
-      </c>
-      <c r="D74" s="7" t="inlineStr">
-        <is>
-          <t>不可</t>
-        </is>
-      </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>C FALSE（DB 既定）</t>
+          <t>○ 進行中（NULL）の判定・重なり判定／U 修正後の終了／C</t>
         </is>
       </c>
       <c r="F74" s="7" t="inlineStr">
         <is>
-          <t>既定 FALSE。Entity のフィールド名は read（getter isRead()）</t>
+          <t>NULL＝進行中。CHECK (end_at &gt;= start_at)。部分ユニーク索引 uq_attendance_breaks_open（進行中は 1 打刻につき 1 件）</t>
         </is>
       </c>
     </row>
@@ -10381,7 +10869,7 @@
         </is>
       </c>
     </row>
-    <row r="76" ht="64" customHeight="1">
+    <row r="76" ht="19" customHeight="1">
       <c r="A76" s="7" t="inlineStr">
         <is>
           <t>updated_at</t>
@@ -10409,77 +10897,377 @@
       </c>
       <c r="F76" s="7" t="inlineStr">
         <is>
+          <t>DB トリガで更新時に自動更新。アプリは設定しない</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="19" customHeight="1">
+      <c r="A77" s="11" t="inlineStr">
+        <is>
+          <t>■ notifications</t>
+        </is>
+      </c>
+      <c r="B77" s="9" t="n"/>
+      <c r="C77" s="9" t="n"/>
+      <c r="D77" s="9" t="n"/>
+      <c r="E77" s="9" t="n"/>
+      <c r="F77" s="10" t="n"/>
+    </row>
+    <row r="78" ht="19" customHeight="1">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>DB列</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>Entityフィールド</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>Java型</t>
+        </is>
+      </c>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="E78" s="6" t="inlineStr">
+        <is>
+          <t>この処理での使用</t>
+        </is>
+      </c>
+      <c r="F78" s="6" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="34" customHeight="1">
+      <c r="A79" s="7" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B79" s="7" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C79" s="7" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="D79" s="7" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="E79" s="7" t="inlineStr">
+        <is>
+          <t>—（INSERT 後に採番）</t>
+        </is>
+      </c>
+      <c r="F79" s="7" t="inlineStr">
+        <is>
+          <t>IDENTITY 自動採番</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="34" customHeight="1">
+      <c r="A80" s="7" t="inlineStr">
+        <is>
+          <t>user_id</t>
+        </is>
+      </c>
+      <c r="B80" s="7" t="inlineStr">
+        <is>
+          <t>userId</t>
+        </is>
+      </c>
+      <c r="C80" s="7" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="D80" s="7" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="E80" s="7" t="inlineStr">
+        <is>
+          <t>C 通知先（申請者／管理者）</t>
+        </is>
+      </c>
+      <c r="F80" s="7" t="inlineStr">
+        <is>
+          <t>FK users（通知先）。登録は NotificationService#notify（ONL-005 定義）</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="49" customHeight="1">
+      <c r="A81" s="7" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="B81" s="7" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="C81" s="7" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="D81" s="7" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="E81" s="7" t="inlineStr">
+        <is>
+          <t>C 登録（REQUEST_APPROVED / REQUEST_SUBMITTED）</t>
+        </is>
+      </c>
+      <c r="F81" s="7" t="inlineStr">
+        <is>
+          <t>VARCHAR(30)。NotificationType の値（REQUEST_SUBMITTED ほか7種。KF-BD-005）</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="34" customHeight="1">
+      <c r="A82" s="7" t="inlineStr">
+        <is>
+          <t>request_id</t>
+        </is>
+      </c>
+      <c r="B82" s="7" t="inlineStr">
+        <is>
+          <t>requestId</t>
+        </is>
+      </c>
+      <c r="C82" s="7" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="D82" s="7" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="E82" s="7" t="inlineStr">
+        <is>
+          <t>C 登録（申請ID）</t>
+        </is>
+      </c>
+      <c r="F82" s="7" t="inlineStr">
+        <is>
+          <t>FK requests(id)。申請に紐づかない通知（LEAVE_*）は NULL</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="19" customHeight="1">
+      <c r="A83" s="7" t="inlineStr">
+        <is>
+          <t>message</t>
+        </is>
+      </c>
+      <c r="B83" s="7" t="inlineStr">
+        <is>
+          <t>message</t>
+        </is>
+      </c>
+      <c r="C83" s="7" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="D83" s="7" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="E83" s="7" t="inlineStr">
+        <is>
+          <t>C 通知本文</t>
+        </is>
+      </c>
+      <c r="F83" s="7" t="inlineStr">
+        <is>
+          <t>VARCHAR(500)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="34" customHeight="1">
+      <c r="A84" s="7" t="inlineStr">
+        <is>
+          <t>is_read</t>
+        </is>
+      </c>
+      <c r="B84" s="7" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="C84" s="7" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="D84" s="7" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="E84" s="7" t="inlineStr">
+        <is>
+          <t>C FALSE（DB 既定）</t>
+        </is>
+      </c>
+      <c r="F84" s="7" t="inlineStr">
+        <is>
+          <t>既定 FALSE。Entity のフィールド名は read（getter isRead()）</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="34" customHeight="1">
+      <c r="A85" s="7" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="B85" s="7" t="inlineStr">
+        <is>
+          <t>createdAt</t>
+        </is>
+      </c>
+      <c r="C85" s="7" t="inlineStr">
+        <is>
+          <t>LocalDateTime</t>
+        </is>
+      </c>
+      <c r="D85" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E85" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F85" s="7" t="inlineStr">
+        <is>
+          <t>DB の DEFAULT。insertable=false, updatable=false</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="64" customHeight="1">
+      <c r="A86" s="7" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+      <c r="B86" s="7" t="inlineStr">
+        <is>
+          <t>updatedAt</t>
+        </is>
+      </c>
+      <c r="C86" s="7" t="inlineStr">
+        <is>
+          <t>LocalDateTime</t>
+        </is>
+      </c>
+      <c r="D86" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E86" s="7" t="inlineStr">
+        <is>
+          <t>— トリガで自動</t>
+        </is>
+      </c>
+      <c r="F86" s="7" t="inlineStr">
+        <is>
           <t>DB トリガ trg_notifications_updated_at（BEFORE UPDATE / set_updated_at）で更新時に自動更新。Entity は insertable=false, updatable=false（アプリは設定しない）</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="8" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="8" t="inlineStr">
         <is>
           <t>7.2 SQL・クエリ</t>
         </is>
       </c>
-      <c r="B78" s="9" t="n"/>
-      <c r="C78" s="9" t="n"/>
-      <c r="D78" s="9" t="n"/>
-      <c r="E78" s="9" t="n"/>
-      <c r="F78" s="10" t="n"/>
-    </row>
-    <row r="79" ht="49" customHeight="1">
-      <c r="A79" s="11" t="inlineStr">
+      <c r="B88" s="9" t="n"/>
+      <c r="C88" s="9" t="n"/>
+      <c r="D88" s="9" t="n"/>
+      <c r="E88" s="9" t="n"/>
+      <c r="F88" s="10" t="n"/>
+    </row>
+    <row r="89" ht="49" customHeight="1">
+      <c r="A89" s="11" t="inlineStr">
         <is>
           <t>実行者・申請者の取得（UserRepository#findById）</t>
         </is>
       </c>
-      <c r="B79" s="12" t="inlineStr">
+      <c r="B89" s="12" t="inlineStr">
         <is>
           <t>SELECT * FROM users WHERE id = ?</t>
         </is>
       </c>
-      <c r="C79" s="9" t="n"/>
-      <c r="D79" s="9" t="n"/>
-      <c r="E79" s="9" t="n"/>
-      <c r="F79" s="10" t="n"/>
-    </row>
-    <row r="80" ht="49" customHeight="1">
-      <c r="A80" s="11" t="inlineStr">
+      <c r="C89" s="9" t="n"/>
+      <c r="D89" s="9" t="n"/>
+      <c r="E89" s="9" t="n"/>
+      <c r="F89" s="10" t="n"/>
+    </row>
+    <row r="90" ht="49" customHeight="1">
+      <c r="A90" s="11" t="inlineStr">
         <is>
           <t>ステップ取得（ApprovalStepRepository#findById）</t>
         </is>
       </c>
-      <c r="B80" s="12" t="inlineStr">
+      <c r="B90" s="12" t="inlineStr">
         <is>
           <t>SELECT * FROM approval_steps WHERE id = ?</t>
         </is>
       </c>
-      <c r="C80" s="9" t="n"/>
-      <c r="D80" s="9" t="n"/>
-      <c r="E80" s="9" t="n"/>
-      <c r="F80" s="10" t="n"/>
-    </row>
-    <row r="81" ht="49" customHeight="1">
-      <c r="A81" s="11" t="inlineStr">
+      <c r="C90" s="9" t="n"/>
+      <c r="D90" s="9" t="n"/>
+      <c r="E90" s="9" t="n"/>
+      <c r="F90" s="10" t="n"/>
+    </row>
+    <row r="91" ht="49" customHeight="1">
+      <c r="A91" s="11" t="inlineStr">
         <is>
           <t>申請取得・行ロック（RequestRepository#findByIdForUpdate）</t>
         </is>
       </c>
-      <c r="B81" s="12" t="inlineStr">
+      <c r="B91" s="12" t="inlineStr">
         <is>
           <t>SELECT * FROM requests WHERE id = ? FOR UPDATE</t>
         </is>
       </c>
-      <c r="C81" s="9" t="n"/>
-      <c r="D81" s="9" t="n"/>
-      <c r="E81" s="9" t="n"/>
-      <c r="F81" s="10" t="n"/>
-    </row>
-    <row r="82" ht="64" customHeight="1">
-      <c r="A82" s="11" t="inlineStr">
+      <c r="C91" s="9" t="n"/>
+      <c r="D91" s="9" t="n"/>
+      <c r="E91" s="9" t="n"/>
+      <c r="F91" s="10" t="n"/>
+    </row>
+    <row r="92" ht="64" customHeight="1">
+      <c r="A92" s="11" t="inlineStr">
         <is>
           <t>ステップ更新（ApprovalStepRepository#actIfWaiting）</t>
         </is>
       </c>
-      <c r="B82" s="12" t="inlineStr">
+      <c r="B92" s="12" t="inlineStr">
         <is>
           <t>UPDATE approval_steps
    SET status = 'APPROVED', approver_id = ?, comment = CAST(? AS VARCHAR(500)),
@@ -10487,84 +11275,84 @@
  WHERE id = ? AND status = 'WAITING'</t>
         </is>
       </c>
-      <c r="C82" s="9" t="n"/>
-      <c r="D82" s="9" t="n"/>
-      <c r="E82" s="9" t="n"/>
-      <c r="F82" s="10" t="n"/>
-    </row>
-    <row r="83" ht="49" customHeight="1">
-      <c r="A83" s="11" t="inlineStr">
+      <c r="C92" s="9" t="n"/>
+      <c r="D92" s="9" t="n"/>
+      <c r="E92" s="9" t="n"/>
+      <c r="F92" s="10" t="n"/>
+    </row>
+    <row r="93" ht="49" customHeight="1">
+      <c r="A93" s="11" t="inlineStr">
         <is>
           <t>1段目承認：次の段へ（RequestRepository#advanceStepIfPending）</t>
         </is>
       </c>
-      <c r="B83" s="12" t="inlineStr">
+      <c r="B93" s="12" t="inlineStr">
         <is>
           <t>UPDATE requests SET current_step = 2
  WHERE id = ? AND status = 'PENDING' AND current_step = 1</t>
         </is>
       </c>
-      <c r="C83" s="9" t="n"/>
-      <c r="D83" s="9" t="n"/>
-      <c r="E83" s="9" t="n"/>
-      <c r="F83" s="10" t="n"/>
-    </row>
-    <row r="84" ht="64" customHeight="1">
-      <c r="A84" s="11" t="inlineStr">
+      <c r="C93" s="9" t="n"/>
+      <c r="D93" s="9" t="n"/>
+      <c r="E93" s="9" t="n"/>
+      <c r="F93" s="10" t="n"/>
+    </row>
+    <row r="94" ht="64" customHeight="1">
+      <c r="A94" s="11" t="inlineStr">
         <is>
           <t>2段目承認：申請確定（RequestRepository#updateStatusIfPending）</t>
         </is>
       </c>
-      <c r="B84" s="12" t="inlineStr">
+      <c r="B94" s="12" t="inlineStr">
         <is>
           <t>UPDATE requests SET status = 'APPROVED'
  WHERE id = ? AND status = 'PENDING' AND current_step = 2</t>
         </is>
       </c>
-      <c r="C84" s="9" t="n"/>
-      <c r="D84" s="9" t="n"/>
-      <c r="E84" s="9" t="n"/>
-      <c r="F84" s="10" t="n"/>
-    </row>
-    <row r="85" ht="79" customHeight="1">
-      <c r="A85" s="11" t="inlineStr">
+      <c r="C94" s="9" t="n"/>
+      <c r="D94" s="9" t="n"/>
+      <c r="E94" s="9" t="n"/>
+      <c r="F94" s="10" t="n"/>
+    </row>
+    <row r="95" ht="79" customHeight="1">
+      <c r="A95" s="11" t="inlineStr">
         <is>
           <t>2段目ステップの取得（通知先解決用。ApprovalStepRepository#findByRequestIdOrderByStepNo）</t>
         </is>
       </c>
-      <c r="B85" s="12" t="inlineStr">
+      <c r="B95" s="12" t="inlineStr">
         <is>
           <t>SELECT * FROM approval_steps WHERE request_id = ? ORDER BY step_no ASC</t>
         </is>
       </c>
-      <c r="C85" s="9" t="n"/>
-      <c r="D85" s="9" t="n"/>
-      <c r="E85" s="9" t="n"/>
-      <c r="F85" s="10" t="n"/>
-    </row>
-    <row r="86" ht="79" customHeight="1">
-      <c r="A86" s="11" t="inlineStr">
+      <c r="C95" s="9" t="n"/>
+      <c r="D95" s="9" t="n"/>
+      <c r="E95" s="9" t="n"/>
+      <c r="F95" s="10" t="n"/>
+    </row>
+    <row r="96" ht="79" customHeight="1">
+      <c r="A96" s="11" t="inlineStr">
         <is>
           <t>有効な管理者の取得（ApprovalRouteService#resolveCurrentApproverIds 内。ONL-005 定義・参考）</t>
         </is>
       </c>
-      <c r="B86" s="12" t="inlineStr">
+      <c r="B96" s="12" t="inlineStr">
         <is>
           <t>SELECT * FROM users WHERE role = 'ADMIN' AND status = 'ACTIVE'   -- 申請者は Java 側で除外</t>
         </is>
       </c>
-      <c r="C86" s="9" t="n"/>
-      <c r="D86" s="9" t="n"/>
-      <c r="E86" s="9" t="n"/>
-      <c r="F86" s="10" t="n"/>
-    </row>
-    <row r="87" ht="79" customHeight="1">
-      <c r="A87" s="11" t="inlineStr">
+      <c r="C96" s="9" t="n"/>
+      <c r="D96" s="9" t="n"/>
+      <c r="E96" s="9" t="n"/>
+      <c r="F96" s="10" t="n"/>
+    </row>
+    <row r="97" ht="79" customHeight="1">
+      <c r="A97" s="11" t="inlineStr">
         <is>
           <t>残日数の消化（LeaveBalanceService#consume 内。ONL-013 定義・参考）</t>
         </is>
       </c>
-      <c r="B87" s="12" t="inlineStr">
+      <c r="B97" s="12" t="inlineStr">
         <is>
           <t>SELECT * FROM leave_types WHERE id = ?;
 SELECT * FROM leave_balances
@@ -10573,158 +11361,182 @@
 UPDATE leave_balances SET used_days = ? WHERE id = ?   -- 行ごと（Entity のダーティチェック）</t>
         </is>
       </c>
-      <c r="C87" s="9" t="n"/>
-      <c r="D87" s="9" t="n"/>
-      <c r="E87" s="9" t="n"/>
-      <c r="F87" s="10" t="n"/>
-    </row>
-    <row r="88" ht="79" customHeight="1">
-      <c r="A88" s="11" t="inlineStr">
+      <c r="C97" s="9" t="n"/>
+      <c r="D97" s="9" t="n"/>
+      <c r="E97" s="9" t="n"/>
+      <c r="F97" s="10" t="n"/>
+    </row>
+    <row r="98" ht="109" customHeight="1">
+      <c r="A98" s="11" t="inlineStr">
         <is>
           <t>打刻の取得・反映（AttendanceRecordRepository）</t>
         </is>
       </c>
-      <c r="B88" s="12" t="inlineStr">
+      <c r="B98" s="12" t="inlineStr">
         <is>
           <t>SELECT * FROM attendance_records WHERE user_id = ? AND work_date = ? FOR UPDATE;
 INSERT INTO attendance_records(user_id, work_date, clock_in, clock_out, work_minutes, overtime_minutes) VALUES (?, ?, ?, ?, ?, ?);   -- 打刻が無い場合
-UPDATE attendance_records SET clock_in = ?, clock_out = ?, work_minutes = ?, overtime_minutes = ? WHERE id = ?   -- 既存の場合</t>
-        </is>
-      </c>
-      <c r="C88" s="9" t="n"/>
-      <c r="D88" s="9" t="n"/>
-      <c r="E88" s="9" t="n"/>
-      <c r="F88" s="10" t="n"/>
-    </row>
-    <row r="89" ht="64" customHeight="1">
-      <c r="A89" s="11" t="inlineStr">
+UPDATE attendance_records SET clock_in = ?, clock_out = ?, work_minutes = ?, overtime_minutes = ? WHERE id = ?   -- 既存の場合
+SELECT * FROM attendance_breaks WHERE attendance_record_id = ? ORDER BY start_at ASC;   -- 打刻修正の再計算用（休憩・離席の区間）</t>
+        </is>
+      </c>
+      <c r="C98" s="9" t="n"/>
+      <c r="D98" s="9" t="n"/>
+      <c r="E98" s="9" t="n"/>
+      <c r="F98" s="10" t="n"/>
+    </row>
+    <row r="99" ht="64" customHeight="1">
+      <c r="A99" s="11" t="inlineStr">
         <is>
           <t>通知登録（NotificationService#notify 内。ONL-005/019 定義・参考）</t>
         </is>
       </c>
-      <c r="B89" s="12" t="inlineStr">
+      <c r="B99" s="12" t="inlineStr">
         <is>
           <t>INSERT INTO notifications (user_id, type, request_id, message, is_read)
   VALUES (?, ?, ?, ?, FALSE)   -- created_at / updated_at は DB の DEFAULT</t>
         </is>
       </c>
-      <c r="C89" s="9" t="n"/>
-      <c r="D89" s="9" t="n"/>
-      <c r="E89" s="9" t="n"/>
-      <c r="F89" s="10" t="n"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="8" t="inlineStr">
+      <c r="C99" s="9" t="n"/>
+      <c r="D99" s="9" t="n"/>
+      <c r="E99" s="9" t="n"/>
+      <c r="F99" s="10" t="n"/>
+    </row>
+    <row r="100" ht="124" customHeight="1">
+      <c r="A100" s="11" t="inlineStr">
+        <is>
+          <t>休憩・離席修正の反映（AttendanceService#applyBreakCorrection。BREAK_CORRECTION の最終承認のみ）</t>
+        </is>
+      </c>
+      <c r="B100" s="12" t="inlineStr">
+        <is>
+          <t>SELECT * FROM attendance_records WHERE user_id = ? AND work_date = ? FOR UPDATE;
+SELECT * FROM attendance_breaks WHERE attendance_record_id = ? ORDER BY start_at ASC;      -- 重なり検証・再計算
+SELECT * FROM attendance_breaks WHERE attendance_record_id = ? AND end_at IS NULL LIMIT 1;  -- 進行中の区間
+UPDATE attendance_breaks SET start_at = ?, end_at = ? WHERE id = ?;                        -- 同種別の進行中区間があれば置換
+INSERT INTO attendance_breaks (attendance_record_id, kind, start_at, end_at) VALUES (?, ?, ?, ?);  -- 無ければ追加
+UPDATE attendance_records SET work_minutes = ?, overtime_minutes = ? WHERE id = ?;         -- clock_out がある場合のみ</t>
+        </is>
+      </c>
+      <c r="C100" s="9" t="n"/>
+      <c r="D100" s="9" t="n"/>
+      <c r="E100" s="9" t="n"/>
+      <c r="F100" s="10" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="8" t="inlineStr">
         <is>
           <t>7.3 設定値</t>
         </is>
       </c>
-      <c r="B91" s="9" t="n"/>
-      <c r="C91" s="9" t="n"/>
-      <c r="D91" s="9" t="n"/>
-      <c r="E91" s="9" t="n"/>
-      <c r="F91" s="10" t="n"/>
-    </row>
-    <row r="92" ht="19" customHeight="1">
-      <c r="A92" s="6" t="inlineStr">
+      <c r="B102" s="9" t="n"/>
+      <c r="C102" s="9" t="n"/>
+      <c r="D102" s="9" t="n"/>
+      <c r="E102" s="9" t="n"/>
+      <c r="F102" s="10" t="n"/>
+    </row>
+    <row r="103" ht="19" customHeight="1">
+      <c r="A103" s="6" t="inlineStr">
         <is>
           <t>キー</t>
         </is>
       </c>
-      <c r="B92" s="6" t="inlineStr">
+      <c r="B103" s="6" t="inlineStr">
         <is>
           <t>格納場所</t>
         </is>
       </c>
-      <c r="C92" s="6" t="inlineStr">
+      <c r="C103" s="6" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D92" s="10" t="n"/>
-      <c r="E92" s="6" t="inlineStr">
+      <c r="D103" s="10" t="n"/>
+      <c r="E103" s="6" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="F92" s="10" t="n"/>
-    </row>
-    <row r="93" ht="49" customHeight="1">
-      <c r="A93" s="7" t="inlineStr">
+      <c r="F103" s="10" t="n"/>
+    </row>
+    <row r="104" ht="49" customHeight="1">
+      <c r="A104" s="7" t="inlineStr">
         <is>
           <t>（Bean）Clock</t>
         </is>
       </c>
-      <c r="B93" s="7" t="inlineStr">
+      <c r="B104" s="7" t="inlineStr">
         <is>
           <t>config/ClockConfig.java</t>
         </is>
       </c>
-      <c r="C93" s="7" t="inlineStr">
+      <c r="C104" s="7" t="inlineStr">
         <is>
           <t>Clock.system(Asia/Tokyo)。業務時刻はこの Bean 経由で取得する</t>
         </is>
       </c>
-      <c r="D93" s="10" t="n"/>
-      <c r="E93" s="7" t="inlineStr">
+      <c r="D104" s="10" t="n"/>
+      <c r="E104" s="7" t="inlineStr">
         <is>
           <t>ONL-002 で定義済み</t>
         </is>
       </c>
-      <c r="F93" s="10" t="n"/>
-    </row>
-    <row r="94" ht="49" customHeight="1">
-      <c r="A94" s="7" t="inlineStr">
+      <c r="F104" s="10" t="n"/>
+    </row>
+    <row r="105" ht="49" customHeight="1">
+      <c r="A105" s="7" t="inlineStr">
         <is>
           <t>spring.jpa.properties.hibernate.jdbc.time_zone</t>
         </is>
       </c>
-      <c r="B94" s="7" t="inlineStr">
+      <c r="B105" s="7" t="inlineStr">
         <is>
           <t>application.properties</t>
         </is>
       </c>
-      <c r="C94" s="7" t="inlineStr">
+      <c r="C105" s="7" t="inlineStr">
         <is>
           <t>Asia/Tokyo。LocalDateTime の DB 読み書きを JST に固定</t>
         </is>
       </c>
-      <c r="D94" s="10" t="n"/>
-      <c r="E94" s="7" t="inlineStr">
+      <c r="D105" s="10" t="n"/>
+      <c r="E105" s="7" t="inlineStr">
         <is>
           <t>ONL-002 で定義済み。JVM オプション -Duser.timezone=Asia/Tokyo も同様</t>
         </is>
       </c>
-      <c r="F94" s="10" t="n"/>
+      <c r="F105" s="10" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="26">
-    <mergeCell ref="C92:D92"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="A56:F56"/>
+  <mergeCells count="28">
+    <mergeCell ref="B91:F91"/>
+    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="B100:F100"/>
+    <mergeCell ref="C104:D104"/>
+    <mergeCell ref="B90:F90"/>
+    <mergeCell ref="B93:F93"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="E92:F92"/>
+    <mergeCell ref="B96:F96"/>
+    <mergeCell ref="A57:F57"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="B86:F86"/>
+    <mergeCell ref="A33:F33"/>
     <mergeCell ref="A14:F14"/>
-    <mergeCell ref="C94:D94"/>
-    <mergeCell ref="E94:F94"/>
-    <mergeCell ref="A32:F32"/>
-    <mergeCell ref="C93:D93"/>
-    <mergeCell ref="A91:F91"/>
-    <mergeCell ref="B88:F88"/>
-    <mergeCell ref="B82:F82"/>
-    <mergeCell ref="B87:F87"/>
-    <mergeCell ref="A67:F67"/>
-    <mergeCell ref="B84:F84"/>
-    <mergeCell ref="B83:F83"/>
-    <mergeCell ref="A45:F45"/>
+    <mergeCell ref="C103:D103"/>
+    <mergeCell ref="E103:F103"/>
+    <mergeCell ref="B98:F98"/>
+    <mergeCell ref="C105:D105"/>
+    <mergeCell ref="E105:F105"/>
+    <mergeCell ref="A68:F68"/>
+    <mergeCell ref="A102:F102"/>
+    <mergeCell ref="E104:F104"/>
+    <mergeCell ref="B99:F99"/>
+    <mergeCell ref="A77:F77"/>
+    <mergeCell ref="B92:F92"/>
+    <mergeCell ref="B95:F95"/>
     <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B79:F79"/>
-    <mergeCell ref="B85:F85"/>
-    <mergeCell ref="E93:F93"/>
-    <mergeCell ref="A78:F78"/>
+    <mergeCell ref="B94:F94"/>
+    <mergeCell ref="A88:F88"/>
+    <mergeCell ref="B97:F97"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
